--- a/docs/pats.xlsx
+++ b/docs/pats.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SA6400</t>
+          <t>RS2423RP+II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA6400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2BII_86009.pat</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA6400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA6400_86009.pat</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -490,12 +490,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA6400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA6400_86003.pat</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA6400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA6400_81180.pat</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA6400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA6400_72806.pat</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,12 +556,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA6400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA6400_69057.pat</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA6400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA6400_64570.pat</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -595,17 +595,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DS1019+</t>
+          <t>SA6400</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1019%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA6400_42962.pat</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1019%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1019%2B_86009.pat</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1019%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1019%2B_42218.pat</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1019%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1019%2B_86003.pat</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1019%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1019%2B_81180.pat</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1019%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1019%2B_72806.pat</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1019%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1019%2B_69057.pat</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1019%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1019%2B_64570.pat</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1019%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1019%2B_42962.pat</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -793,17 +793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DS1520+</t>
+          <t>DS1019+</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1520%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1019%2B_42661.pat</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1520%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1520%2B_86009.pat</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1520%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1520%2B_42218.pat</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1520%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1520%2B_86003.pat</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1520%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1520%2B_81180.pat</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1520%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1520%2B_72806.pat</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1520%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1520%2B_69057.pat</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1520%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1520%2B_64570.pat</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1520%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1520%2B_42962.pat</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -991,17 +991,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DS1522+</t>
+          <t>DS1520+</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1522%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1520%2B_42661.pat</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1522%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1522%2B_86009.pat</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1522%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1522%2B_86003.pat</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1522%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1522%2B_81180.pat</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1522%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1522%2B_72806.pat</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1522%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1522%2B_69057.pat</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1522%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1522%2B_64570.pat</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1145,17 +1145,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DS1525+</t>
+          <t>DS1522+</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1525%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1522%2B_42962.pat</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1525%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1525%2B_86009.pat</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1525%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1525%2B_86003.pat</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1525%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1525%2B_81180.pat</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DS1621+</t>
+          <t>DS1525+</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1525%2B_72806.pat</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621%2B_86009.pat</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621%2B_42218.pat</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621%2B_86003.pat</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621%2B_81180.pat</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621%2B_72806.pat</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621%2B_69057.pat</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621%2B_64570.pat</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621%2B_42962.pat</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1431,17 +1431,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DS1621xs+</t>
+          <t>DS1621+</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621%2B_42661.pat</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1629,17 +1629,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DS1819+</t>
+          <t>DS1621xs+</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1819%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1819%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1819%2B_86009.pat</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1819%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1819%2B_42218.pat</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1819%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1819%2B_86003.pat</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1819%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1819%2B_81180.pat</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1819%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1819%2B_72806.pat</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1819%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1819%2B_69057.pat</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1819%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1819%2B_64570.pat</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1819%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1819%2B_42962.pat</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1827,17 +1827,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DS1821+</t>
+          <t>DS1819+</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1821%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1819%2B_42661.pat</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1821%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1821%2B_86009.pat</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1821%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1821%2B_42218.pat</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1821%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1821%2B_86003.pat</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1821%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1821%2B_81180.pat</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1821%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1821%2B_72806.pat</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1821%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1821%2B_69057.pat</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1821%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1821%2B_64570.pat</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1821%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1821%2B_42962.pat</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2025,17 +2025,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DS1823xs+</t>
+          <t>DS1821+</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1823xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1821%2B_42661.pat</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1823xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1823xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1823xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1823xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1823xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1823xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1823xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1823xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1823xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1823xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS1823xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1823xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2179,17 +2179,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DS1825+</t>
+          <t>DS1823xs+</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1825%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS1823xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1825%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1825%2B_86009.pat</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1825%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1825%2B_86003.pat</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1825%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1825%2B_81180.pat</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2267,17 +2267,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DS220+</t>
+          <t>DS1825+</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS220%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1825%2B_72806.pat</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS220%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS220%2B_86009.pat</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS220%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS220%2B_42218.pat</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS220%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS220%2B_86003.pat</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS220%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS220%2B_81180.pat</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS220%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS220%2B_72806.pat</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS220%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS220%2B_69057.pat</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS220%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS220%2B_64570.pat</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS220%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS220%2B_42962.pat</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2465,17 +2465,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DS224+</t>
+          <t>DS220+</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS224%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS220%2B_42661.pat</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS224%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS224%2B_86009.pat</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS224%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS224%2B_86003.pat</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS224%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS224%2B_81180.pat</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS224%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS224%2B_72806.pat</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2575,17 +2575,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DS225+</t>
+          <t>DS224+</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS225%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS224%2B_69057.pat</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS225%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS225%2B_86009.pat</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS225%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS225%2B_86003.pat</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS225%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS225%2B_81180.pat</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2663,17 +2663,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DS2419+</t>
+          <t>DS225+</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS225%2B_72806.pat</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2B_86009.pat</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2B_42218.pat</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2B_86003.pat</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2B_81180.pat</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2B_72806.pat</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2B_69057.pat</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2B_64570.pat</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2B_42962.pat</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2861,17 +2861,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DS2419+II</t>
+          <t>DS2419+</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2BII_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2B_42661.pat</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2BII_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2BII_86009.pat</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2BII_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2BII_42218.pat</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2BII_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2BII_86003.pat</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2BII_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2BII_81180.pat</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2BII_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2BII_72806.pat</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2BII_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2BII_69057.pat</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2BII_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2BII_64570.pat</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2BII_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2BII_42962.pat</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3059,17 +3059,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DS2422+</t>
+          <t>DS2419+II</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2422%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2BII_42661.pat</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2422%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2422%2B_86009.pat</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2422%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2422%2B_86003.pat</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2422%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2422%2B_81180.pat</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2422%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2422%2B_72806.pat</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2422%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2422%2B_69057.pat</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2422%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2422%2B_64570.pat</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2422%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2422%2B_42962.pat</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2422%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2422%2B_42661.pat</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3257,17 +3257,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DS3622xs+</t>
+          <t>DS2422+</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3622xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2422%2B_42218.pat</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3622xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3622xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3622xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3622xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3622xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3622xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3622xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3622xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3622xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3622xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3622xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3622xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3622xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3622xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3622xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3622xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3455,17 +3455,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DS420+</t>
+          <t>DS3622xs+</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS420%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3622xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS420%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS420%2B_86009.pat</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS420%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS420%2B_42218.pat</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS420%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS420%2B_86003.pat</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS420%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS420%2B_81180.pat</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS420%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS420%2B_72806.pat</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS420%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS420%2B_69057.pat</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS420%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS420%2B_64570.pat</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS420%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS420%2B_42962.pat</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3653,17 +3653,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DS423+</t>
+          <t>DS420+</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS423%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS420%2B_42661.pat</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS423%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS423%2B_86009.pat</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS423%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS423%2B_86003.pat</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS423%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS423%2B_81180.pat</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS423%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS423%2B_72806.pat</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS423%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS423%2B_69057.pat</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS423%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS423%2B_64570.pat</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3807,17 +3807,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DS425+</t>
+          <t>DS423+</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS425%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS423%2B_42962.pat</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS425%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS425%2B_86009.pat</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS425%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS425%2B_86003.pat</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS425%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS425%2B_81180.pat</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3895,17 +3895,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DS620slim</t>
+          <t>DS425+</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS620slim_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS425%2B_72806.pat</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS620slim_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS620slim_86009.pat</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS620slim_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS620slim_42218.pat</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS620slim_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS620slim_86003.pat</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS620slim_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS620slim_81180.pat</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_DS620slim_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS620slim_72806.pat</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS620slim_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_DS620slim_69057.pat</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS620slim_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS620slim_64570.pat</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS620slim_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS620slim_42962.pat</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4093,17 +4093,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DS720+</t>
+          <t>DS620slim</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS720%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS620slim_42661.pat</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS720%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS720%2B_86009.pat</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS720%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS720%2B_42218.pat</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS720%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS720%2B_86003.pat</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS720%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS720%2B_81180.pat</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS720%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS720%2B_72806.pat</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS720%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS720%2B_69057.pat</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS720%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS720%2B_64570.pat</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS720%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS720%2B_42962.pat</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4291,17 +4291,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DS723+</t>
+          <t>DS720+</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS723%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS720%2B_42661.pat</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS723%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS723%2B_86009.pat</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS723%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS723%2B_86003.pat</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS723%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS723%2B_81180.pat</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS723%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS723%2B_72806.pat</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS723%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS723%2B_69057.pat</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS723%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS723%2B_64570.pat</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4445,17 +4445,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DS725+</t>
+          <t>DS723+</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS725%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS723%2B_42962.pat</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4472,12 +4472,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS725%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS725%2B_86009.pat</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS725%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS725%2B_86003.pat</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS725%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS725%2B_81180.pat</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4533,17 +4533,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DS920+</t>
+          <t>DS725+</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS920%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS725%2B_72806.pat</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS920%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS920%2B_86009.pat</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS920%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS920%2B_42218.pat</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS920%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS920%2B_86003.pat</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS920%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS920%2B_81180.pat</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS920%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS920%2B_72806.pat</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS920%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS920%2B_69057.pat</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS920%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS920%2B_64570.pat</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS920%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS920%2B_42962.pat</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4731,17 +4731,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>DS923+</t>
+          <t>DS920+</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS923%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS920%2B_42661.pat</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS923%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS923%2B_86009.pat</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS923%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS923%2B_86003.pat</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS923%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS923%2B_81180.pat</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS923%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS923%2B_72806.pat</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS923%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS923%2B_69057.pat</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS923%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS923%2B_64570.pat</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4885,17 +4885,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DS925+</t>
+          <t>DS923+</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS925%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS923%2B_42962.pat</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS925%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS925%2B_86009.pat</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS925%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS925%2B_86003.pat</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS925%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS925%2B_81180.pat</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4973,17 +4973,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>DVA1622</t>
+          <t>DS925+</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA1622_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS925%2B_72806.pat</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA1622_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA1622_86009.pat</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA1622_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA1622_86003.pat</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA1622_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA1622_81180.pat</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA1622_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA1622_72806.pat</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA1622_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA1622_69057.pat</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA1622_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA1622_64570.pat</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5127,17 +5127,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>DVA3219</t>
+          <t>DVA1622</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3219_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA1622_42962.pat</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3219_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3219_86009.pat</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3219_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3219_42218.pat</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3219_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3219_86003.pat</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3219_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3219_81180.pat</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3219_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3219_72806.pat</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3219_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3219_69057.pat</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3219_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3219_64570.pat</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3219_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3219_42962.pat</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5325,17 +5325,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>DVA3221</t>
+          <t>DVA3219</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3221_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3219_42661.pat</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3221_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3221_86009.pat</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3221_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3221_42218.pat</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3221_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3221_86003.pat</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3221_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3221_81180.pat</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3221_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3221_72806.pat</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3221_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3221_69057.pat</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3221_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3221_64570.pat</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3221_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3221_42962.pat</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5523,17 +5523,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FS2500</t>
+          <t>DVA3221</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2500_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3221_42661.pat</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2500_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2500_86009.pat</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2500_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2500_86003.pat</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2500_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2500_81180.pat</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2500_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2500_72806.pat</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2500_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2500_69057.pat</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5660,12 +5660,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2500_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2500_64570.pat</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2500_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2500_42962.pat</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2500_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2500_42661.pat</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -5721,17 +5721,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FS3400</t>
+          <t>FS2500</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2500_42218.pat</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3400_86009.pat</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3400_42218.pat</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3400_86003.pat</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3400_81180.pat</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3400_72806.pat</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3400_69057.pat</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3400_64570.pat</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3400_42962.pat</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -5919,17 +5919,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FS3410</t>
+          <t>FS3400</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3410_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3400_42661.pat</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3410_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3410_86009.pat</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3410_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3410_86003.pat</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3410_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3410_81180.pat</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3410_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3410_72806.pat</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3410_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3410_69057.pat</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3410_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3410_64570.pat</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6073,17 +6073,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FS3600</t>
+          <t>FS3410</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3410_42962.pat</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -6271,17 +6271,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FS6400</t>
+          <t>FS3600</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -6469,17 +6469,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>HD6500</t>
+          <t>FS6400</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_HD6500_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_HD6500_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_HD6500_86009.pat</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_HD6500_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_HD6500_86003.pat</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_HD6500_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_HD6500_81180.pat</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_HD6500_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_HD6500_72806.pat</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_HD6500_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_HD6500_69057.pat</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_HD6500_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_HD6500_64570.pat</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6623,17 +6623,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>RS1221+</t>
+          <t>HD6500</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_HD6500_42962.pat</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221%2B_86009.pat</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221%2B_42218.pat</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221%2B_86003.pat</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221%2B_81180.pat</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221%2B_72806.pat</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221%2B_69057.pat</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221%2B_64570.pat</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221%2B_42962.pat</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6821,17 +6821,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>RS1221RP+</t>
+          <t>RS1221+</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221%2B_42661.pat</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7019,17 +7019,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>RS1619xs+</t>
+          <t>RS1221RP+</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1619xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1619xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1619xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1619xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1619xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1619xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1619xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1619xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1619xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1619xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1619xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1619xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1619xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1619xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1619xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7200,12 +7200,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1619xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1619xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7217,17 +7217,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>RS2421+</t>
+          <t>RS1619xs+</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1619xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421%2B_86009.pat</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421%2B_42218.pat</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421%2B_86003.pat</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421%2B_81180.pat</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7332,12 +7332,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421%2B_72806.pat</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421%2B_69057.pat</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421%2B_64570.pat</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421%2B_42962.pat</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7415,17 +7415,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>RS2421RP+</t>
+          <t>RS2421+</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421%2B_42661.pat</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -7613,17 +7613,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>RS2423+</t>
+          <t>RS2421RP+</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423%2B_86009.pat</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423%2B_86003.pat</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -7684,12 +7684,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423%2B_81180.pat</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423%2B_72806.pat</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423%2B_69057.pat</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423%2B_64570.pat</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -7767,17 +7767,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>RS2423RP+</t>
+          <t>RS2423+</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423%2B_42962.pat</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -7794,12 +7794,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -7921,17 +7921,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>RS2423RP+II</t>
+          <t>RS2423RP+</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2BII_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">

--- a/docs/pats.xlsx
+++ b/docs/pats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D629"/>
+  <dimension ref="A1:D628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RS2423RP+II</t>
+          <t>SA6400</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2BII_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA6400_86009.pat</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA6400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA6400_86003.pat</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -490,12 +490,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA6400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA6400_81180.pat</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA6400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA6400_72806.pat</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA6400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA6400_69057.pat</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,12 +556,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA6400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA6400_64570.pat</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA6400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA6400_42962.pat</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -595,17 +595,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SA6400</t>
+          <t>DS1019+</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA6400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1019%2B_86009.pat</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1019%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1019%2B_42218.pat</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1019%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1019%2B_86003.pat</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1019%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1019%2B_81180.pat</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1019%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1019%2B_72806.pat</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1019%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1019%2B_69057.pat</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1019%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1019%2B_64570.pat</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1019%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1019%2B_42962.pat</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1019%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1019%2B_42661.pat</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -793,17 +793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DS1019+</t>
+          <t>DS1520+</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1019%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1520%2B_86009.pat</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1520%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1520%2B_42218.pat</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1520%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1520%2B_86003.pat</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1520%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1520%2B_81180.pat</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1520%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1520%2B_72806.pat</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1520%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1520%2B_69057.pat</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1520%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1520%2B_64570.pat</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1520%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1520%2B_42962.pat</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1520%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1520%2B_42661.pat</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -991,17 +991,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DS1520+</t>
+          <t>DS1522+</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1520%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1522%2B_86009.pat</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1522%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1522%2B_86003.pat</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1522%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1522%2B_81180.pat</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1522%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1522%2B_72806.pat</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1522%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1522%2B_69057.pat</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1522%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1522%2B_64570.pat</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1522%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1522%2B_42962.pat</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1145,17 +1145,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DS1522+</t>
+          <t>DS1525+</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1522%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1525%2B_86009.pat</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1525%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1525%2B_86003.pat</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1525%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1525%2B_81180.pat</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1525%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1525%2B_72806.pat</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DS1525+</t>
+          <t>DS1621+</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1525%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621%2B_86009.pat</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621%2B_42218.pat</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621%2B_86003.pat</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621%2B_81180.pat</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621%2B_72806.pat</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621%2B_69057.pat</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621%2B_64570.pat</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621%2B_42962.pat</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621%2B_42661.pat</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1431,17 +1431,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DS1621+</t>
+          <t>DS1621xs+</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1629,17 +1629,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DS1621xs+</t>
+          <t>DS1819+</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1819%2B_86009.pat</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1819%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1819%2B_42218.pat</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1819%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1819%2B_86003.pat</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1819%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1819%2B_81180.pat</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1819%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1819%2B_72806.pat</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1819%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1819%2B_69057.pat</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1819%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1819%2B_64570.pat</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1819%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1819%2B_42962.pat</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1819%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1819%2B_42661.pat</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1827,17 +1827,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DS1819+</t>
+          <t>DS1821+</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1819%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1821%2B_86009.pat</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1821%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1821%2B_42218.pat</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1821%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1821%2B_86003.pat</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1821%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1821%2B_81180.pat</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1821%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1821%2B_72806.pat</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1821%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1821%2B_69057.pat</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1821%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1821%2B_64570.pat</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1821%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1821%2B_42962.pat</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1821%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1821%2B_42661.pat</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2025,17 +2025,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DS1821+</t>
+          <t>DS1823xs+</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1821%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1823xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1823xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1823xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1823xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1823xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1823xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1823xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1823xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1823xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1823xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1823xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1823xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS1823xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2179,17 +2179,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DS1823xs+</t>
+          <t>DS1825+</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS1823xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1825%2B_86009.pat</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1825%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1825%2B_86003.pat</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1825%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1825%2B_81180.pat</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1825%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1825%2B_72806.pat</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2267,17 +2267,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DS1825+</t>
+          <t>DS220+</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1825%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS220%2B_86009.pat</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS220%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS220%2B_42218.pat</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS220%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS220%2B_86003.pat</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS220%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS220%2B_81180.pat</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS220%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS220%2B_72806.pat</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS220%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS220%2B_69057.pat</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS220%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS220%2B_64570.pat</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS220%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS220%2B_42962.pat</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS220%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS220%2B_42661.pat</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2465,17 +2465,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DS220+</t>
+          <t>DS224+</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS220%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS224%2B_86009.pat</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS224%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS224%2B_86003.pat</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS224%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS224%2B_81180.pat</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS224%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS224%2B_72806.pat</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS224%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS224%2B_69057.pat</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2575,17 +2575,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DS224+</t>
+          <t>DS225+</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS224%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS225%2B_86009.pat</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS225%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS225%2B_86003.pat</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS225%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS225%2B_81180.pat</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS225%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS225%2B_72806.pat</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2663,17 +2663,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DS225+</t>
+          <t>DS2419+</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS225%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2B_86009.pat</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2B_42218.pat</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2B_86003.pat</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2B_81180.pat</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2B_72806.pat</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2B_69057.pat</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2B_64570.pat</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2B_42962.pat</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2B_42661.pat</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2861,17 +2861,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DS2419+</t>
+          <t>DS2419+II</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2BII_86009.pat</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2BII_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2BII_42218.pat</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2BII_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2BII_86003.pat</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2BII_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2BII_81180.pat</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2BII_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2BII_72806.pat</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2BII_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2BII_69057.pat</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2BII_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2BII_64570.pat</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2BII_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2BII_42962.pat</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2BII_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2BII_42661.pat</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3059,17 +3059,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DS2419+II</t>
+          <t>DS2422+</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2BII_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2422%2B_86009.pat</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2422%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2422%2B_86003.pat</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2422%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2422%2B_81180.pat</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2422%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2422%2B_72806.pat</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2422%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2422%2B_69057.pat</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2422%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2422%2B_64570.pat</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2422%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2422%2B_42962.pat</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2422%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2422%2B_42661.pat</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2422%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2422%2B_42218.pat</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3257,17 +3257,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DS2422+</t>
+          <t>DS3622xs+</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2422%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3622xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3622xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3622xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3622xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3622xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3622xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3622xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3622xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3622xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3622xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3622xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3622xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3622xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3622xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3622xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3622xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3622xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3455,17 +3455,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DS3622xs+</t>
+          <t>DS420+</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3622xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS420%2B_86009.pat</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS420%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS420%2B_42218.pat</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS420%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS420%2B_86003.pat</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS420%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS420%2B_81180.pat</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS420%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS420%2B_72806.pat</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS420%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS420%2B_69057.pat</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS420%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS420%2B_64570.pat</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS420%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS420%2B_42962.pat</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS420%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS420%2B_42661.pat</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3653,17 +3653,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DS420+</t>
+          <t>DS423+</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS420%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS423%2B_86009.pat</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS423%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS423%2B_86003.pat</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS423%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS423%2B_81180.pat</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS423%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS423%2B_72806.pat</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS423%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS423%2B_69057.pat</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS423%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS423%2B_64570.pat</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS423%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS423%2B_42962.pat</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3807,17 +3807,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DS423+</t>
+          <t>DS425+</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS423%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS425%2B_86009.pat</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS425%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS425%2B_86003.pat</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS425%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS425%2B_81180.pat</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS425%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS425%2B_72806.pat</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3895,17 +3895,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DS425+</t>
+          <t>DS620slim</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS425%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS620slim_86009.pat</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS620slim_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS620slim_42218.pat</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS620slim_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS620slim_86003.pat</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS620slim_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS620slim_81180.pat</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS620slim_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS620slim_72806.pat</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS620slim_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_DS620slim_69057.pat</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_DS620slim_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS620slim_64570.pat</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS620slim_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS620slim_42962.pat</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS620slim_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS620slim_42661.pat</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4093,17 +4093,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DS620slim</t>
+          <t>DS720+</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS620slim_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS720%2B_86009.pat</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS720%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS720%2B_42218.pat</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS720%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS720%2B_86003.pat</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS720%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS720%2B_81180.pat</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS720%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS720%2B_72806.pat</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS720%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS720%2B_69057.pat</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS720%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS720%2B_64570.pat</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS720%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS720%2B_42962.pat</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS720%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS720%2B_42661.pat</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4291,17 +4291,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DS720+</t>
+          <t>DS723+</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS720%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS723%2B_86009.pat</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS723%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS723%2B_86003.pat</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS723%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS723%2B_81180.pat</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS723%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS723%2B_72806.pat</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS723%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS723%2B_69057.pat</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS723%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS723%2B_64570.pat</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS723%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS723%2B_42962.pat</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4445,17 +4445,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DS723+</t>
+          <t>DS725+</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS723%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS725%2B_86009.pat</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4472,12 +4472,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS725%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS725%2B_86003.pat</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS725%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS725%2B_81180.pat</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS725%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS725%2B_72806.pat</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4533,17 +4533,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DS725+</t>
+          <t>DS920+</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS725%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS920%2B_86009.pat</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS920%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS920%2B_42218.pat</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS920%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS920%2B_86003.pat</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS920%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS920%2B_81180.pat</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS920%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS920%2B_72806.pat</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS920%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS920%2B_69057.pat</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS920%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS920%2B_64570.pat</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS920%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS920%2B_42962.pat</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS920%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS920%2B_42661.pat</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4731,17 +4731,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>DS920+</t>
+          <t>DS923+</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS920%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS923%2B_86009.pat</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS923%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS923%2B_86003.pat</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS923%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS923%2B_81180.pat</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS923%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS923%2B_72806.pat</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS923%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS923%2B_69057.pat</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS923%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS923%2B_64570.pat</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS923%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS923%2B_42962.pat</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4885,17 +4885,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DS923+</t>
+          <t>DS925+</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS923%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS925%2B_86009.pat</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS925%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS925%2B_86003.pat</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS925%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS925%2B_81180.pat</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS925%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS925%2B_72806.pat</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4973,17 +4973,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>DS925+</t>
+          <t>DVA1622</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS925%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA1622_86009.pat</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA1622_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA1622_86003.pat</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA1622_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA1622_81180.pat</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA1622_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA1622_72806.pat</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA1622_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA1622_69057.pat</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA1622_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA1622_64570.pat</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA1622_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA1622_42962.pat</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5127,17 +5127,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>DVA1622</t>
+          <t>DVA3219</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA1622_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3219_86009.pat</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3219_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3219_42218.pat</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3219_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3219_86003.pat</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3219_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3219_81180.pat</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3219_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3219_72806.pat</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3219_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3219_69057.pat</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3219_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3219_64570.pat</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3219_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3219_42962.pat</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3219_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3219_42661.pat</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5325,17 +5325,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>DVA3219</t>
+          <t>DVA3221</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3219_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3221_86009.pat</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3221_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3221_42218.pat</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3221_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3221_86003.pat</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3221_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3221_81180.pat</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3221_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3221_72806.pat</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3221_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3221_69057.pat</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3221_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3221_64570.pat</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3221_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3221_42962.pat</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3221_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3221_42661.pat</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5523,17 +5523,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DVA3221</t>
+          <t>FS2500</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3221_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2500_86009.pat</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2500_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2500_86003.pat</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2500_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2500_81180.pat</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2500_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2500_72806.pat</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2500_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2500_69057.pat</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2500_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2500_64570.pat</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5660,12 +5660,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2500_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2500_42962.pat</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2500_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2500_42661.pat</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2500_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2500_42218.pat</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -5721,17 +5721,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FS2500</t>
+          <t>FS3400</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2500_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3400_86009.pat</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3400_42218.pat</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3400_86003.pat</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3400_81180.pat</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3400_72806.pat</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3400_69057.pat</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3400_64570.pat</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3400_42962.pat</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3400_42661.pat</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -5919,17 +5919,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FS3400</t>
+          <t>FS3410</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3410_86009.pat</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3410_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3410_86003.pat</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3410_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3410_81180.pat</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3410_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3410_72806.pat</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3410_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3410_69057.pat</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3410_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3410_64570.pat</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3410_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3410_42962.pat</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6073,17 +6073,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FS3410</t>
+          <t>FS3600</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3410_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -6271,17 +6271,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FS3600</t>
+          <t>FS6400</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -6469,17 +6469,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>FS6400</t>
+          <t>HD6500</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_HD6500_86009.pat</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_HD6500_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_HD6500_86003.pat</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_HD6500_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_HD6500_81180.pat</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_HD6500_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_HD6500_72806.pat</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_HD6500_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_HD6500_69057.pat</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_HD6500_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_HD6500_64570.pat</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_HD6500_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_HD6500_42962.pat</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6623,17 +6623,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>HD6500</t>
+          <t>RS1221+</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_HD6500_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221%2B_86009.pat</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221%2B_42218.pat</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221%2B_86003.pat</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221%2B_81180.pat</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221%2B_72806.pat</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221%2B_69057.pat</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221%2B_64570.pat</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221%2B_42962.pat</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221%2B_42661.pat</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6821,17 +6821,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>RS1221+</t>
+          <t>RS1221RP+</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7019,17 +7019,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>RS1221RP+</t>
+          <t>RS1619xs+</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1619xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1619xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1619xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1619xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1619xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1619xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1619xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1619xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1619xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1619xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1619xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1619xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1619xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1619xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1619xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7200,12 +7200,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1619xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1619xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7217,17 +7217,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>RS1619xs+</t>
+          <t>RS2421+</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1619xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421%2B_86009.pat</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421%2B_42218.pat</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421%2B_86003.pat</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421%2B_81180.pat</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421%2B_72806.pat</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7332,12 +7332,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421%2B_69057.pat</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421%2B_64570.pat</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421%2B_42962.pat</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421%2B_42661.pat</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7415,17 +7415,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>RS2421+</t>
+          <t>RS2421RP+</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -7613,17 +7613,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>RS2421RP+</t>
+          <t>RS2423+</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423%2B_86009.pat</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423%2B_86003.pat</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423%2B_81180.pat</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -7684,12 +7684,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423%2B_72806.pat</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423%2B_69057.pat</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423%2B_64570.pat</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423%2B_42962.pat</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -7767,17 +7767,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>RS2423+</t>
+          <t>RS2423RP+</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -7794,12 +7794,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -7921,17 +7921,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>RS2423RP+</t>
+          <t>RS2821RP+</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2821RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2821RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2821RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2821RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2821RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2821RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2821RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2821RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2821RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2821RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2821RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2821RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2821RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2821RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2821RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2821RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2821RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -8119,17 +8119,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>RS2821RP+</t>
+          <t>RS2825RP+</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2821RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2825RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2825RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2825RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2825RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2825RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2825RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2825RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -8207,17 +8207,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>RS2825RP+</t>
+          <t>RS3618xs</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2825RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3618xs_86009.pat</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3618xs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3618xs_42218.pat</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3618xs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3618xs_86003.pat</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3618xs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3618xs_81180.pat</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3618xs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3618xs_72806.pat</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3618xs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3618xs_69057.pat</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -8344,12 +8344,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3618xs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3618xs_64570.pat</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3618xs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3618xs_42962.pat</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3618xs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3618xs_42661.pat</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -8405,17 +8405,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>RS3618xs</t>
+          <t>RS3621RPxs</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3618xs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621RPxs_86009.pat</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621RPxs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621RPxs_42218.pat</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621RPxs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621RPxs_86003.pat</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621RPxs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621RPxs_81180.pat</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621RPxs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621RPxs_72806.pat</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621RPxs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621RPxs_69057.pat</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621RPxs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621RPxs_64570.pat</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621RPxs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621RPxs_42962.pat</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621RPxs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621RPxs_42661.pat</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -8603,17 +8603,17 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>RS3621RPxs</t>
+          <t>RS3621xs+</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621RPxs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -8801,17 +8801,17 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>RS3621xs+</t>
+          <t>RS4021xs+</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4021xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4021xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4021xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4021xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4021xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4021xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4021xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4021xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4021xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4021xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4021xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4021xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4021xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4021xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4021xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4021xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4021xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -8999,17 +8999,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>RS4021xs+</t>
+          <t>RS422+</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4021xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS422%2B_86009.pat</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS422%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS422%2B_86003.pat</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS422%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS422%2B_81180.pat</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS422%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS422%2B_72806.pat</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS422%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS422%2B_69057.pat</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -9114,12 +9114,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS422%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS422%2B_64570.pat</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS422%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS422%2B_42962.pat</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -9153,17 +9153,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>RS422+</t>
+          <t>RS820+</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS422%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820%2B_86009.pat</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820%2B_42218.pat</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820%2B_86003.pat</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -9224,12 +9224,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820%2B_81180.pat</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -9246,12 +9246,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820%2B_72806.pat</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -9268,12 +9268,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820%2B_69057.pat</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820%2B_64570.pat</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820%2B_42962.pat</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820%2B_42661.pat</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -9351,17 +9351,17 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>RS820+</t>
+          <t>RS820RP+</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -9532,12 +9532,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -9549,17 +9549,17 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>RS820RP+</t>
+          <t>RS822+</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822%2B_86009.pat</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822%2B_86003.pat</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -9598,12 +9598,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822%2B_72806.pat</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822%2B_69057.pat</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822%2B_64570.pat</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822%2B_42962.pat</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -9681,17 +9681,17 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>RS822+</t>
+          <t>RS822RP+</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -9813,17 +9813,17 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>RS822RP+</t>
+          <t>SA3200D</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3200D_86009.pat</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3200D_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3200D_42218.pat</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3200D_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3200D_86003.pat</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3200D_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3200D_81180.pat</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3200D_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3200D_72806.pat</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3200D_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3200D_69057.pat</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3200D_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3200D_64570.pat</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3200D_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3200D_42962.pat</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3200D_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3200D_42661.pat</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -10011,17 +10011,17 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>SA3200D</t>
+          <t>SA3400</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3200D_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400_86009.pat</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -10038,12 +10038,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3400_42218.pat</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400_86003.pat</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -10082,12 +10082,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400_81180.pat</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400_72806.pat</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400_69057.pat</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400_64570.pat</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3400_42962.pat</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3400_42661.pat</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -10209,17 +10209,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>SA3400</t>
+          <t>SA3400D</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400D_86009.pat</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400D_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400D_86003.pat</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400D_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400D_81180.pat</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -10280,12 +10280,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400D_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400D_72806.pat</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400D_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400D_69057.pat</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400D_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400D_64570.pat</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400D_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3400D_42962.pat</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -10363,17 +10363,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>SA3400D</t>
+          <t>SA3410</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3400D_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3410_86009.pat</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3410_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3410_86003.pat</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -10412,12 +10412,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3410_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3410_81180.pat</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3410_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3410_72806.pat</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -10456,12 +10456,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3410_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3410_69057.pat</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3410_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3410_64570.pat</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -10500,12 +10500,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3410_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3410_42962.pat</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -10517,17 +10517,17 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>SA3410</t>
+          <t>SA3600</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3410_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3600_86009.pat</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -10544,12 +10544,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3600_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3600_42218.pat</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3600_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3600_86003.pat</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3600_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3600_81180.pat</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -10610,12 +10610,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3600_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3600_72806.pat</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3600_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3600_69057.pat</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3600_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3600_64570.pat</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3600_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3600_42962.pat</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3600_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3600_42661.pat</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -10715,17 +10715,17 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>SA3600</t>
+          <t>SA3610</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3600_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3610_86009.pat</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3610_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3610_86003.pat</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3610_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3610_81180.pat</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3610_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3610_72806.pat</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3610_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3610_69057.pat</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3610_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3610_64570.pat</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3610_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3610_42962.pat</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -10869,17 +10869,17 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>SA3610</t>
+          <t>DS1618+</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3610_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1618%2B_86009.pat</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1618%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1618%2B_42218.pat</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1618%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1618%2B_86003.pat</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -10940,12 +10940,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1618%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1618%2B_81180.pat</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1618%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1618%2B_72806.pat</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1618%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1618%2B_69057.pat</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1618%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1618%2B_64570.pat</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1618%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1618%2B_42962.pat</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1618%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1618%2B_42661.pat</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -11067,17 +11067,17 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>DS1618+</t>
+          <t>DS218+</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1618%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS218%2B_86009.pat</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -11094,12 +11094,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS218%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS218%2B_42218.pat</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS218%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS218%2B_86003.pat</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS218%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS218%2B_81180.pat</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -11160,12 +11160,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS218%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS218%2B_72806.pat</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -11182,12 +11182,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS218%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS218%2B_69057.pat</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS218%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS218%2B_64570.pat</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -11226,12 +11226,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS218%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS218%2B_42962.pat</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS218%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS218%2B_42661.pat</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -11265,17 +11265,17 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>DS218+</t>
+          <t>DS3018xs</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS218%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3018xs_86009.pat</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -11292,12 +11292,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3018xs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3018xs_42218.pat</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -11314,12 +11314,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3018xs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3018xs_86003.pat</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3018xs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3018xs_81180.pat</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3018xs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3018xs_72806.pat</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3018xs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3018xs_69057.pat</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -11402,12 +11402,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3018xs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3018xs_64570.pat</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3018xs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3018xs_42962.pat</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3018xs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3018xs_42661.pat</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -11463,17 +11463,17 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>DS3018xs</t>
+          <t>DS3617xs</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3018xs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xs_86009.pat</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xs_42218.pat</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xs_86003.pat</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xs_81180.pat</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -11556,12 +11556,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xs_72806.pat</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xs_69057.pat</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -11600,12 +11600,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xs_64570.pat</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xs_42962.pat</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -11644,12 +11644,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xs_42661.pat</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -11661,17 +11661,17 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>DS3617xs</t>
+          <t>DS3617xsII</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xsII_86009.pat</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -11688,12 +11688,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xsII_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xsII_42218.pat</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -11710,12 +11710,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xsII_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xsII_86003.pat</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -11732,12 +11732,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xsII_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xsII_81180.pat</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xsII_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xsII_72806.pat</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xsII_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xsII_69057.pat</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xsII_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xsII_64570.pat</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xsII_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xsII_42962.pat</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xsII_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xsII_42661.pat</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -11859,17 +11859,17 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>DS3617xsII</t>
+          <t>DS418play</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xsII_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS418play_86009.pat</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -11886,12 +11886,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS418play_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS418play_42218.pat</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS418play_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS418play_86003.pat</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS418play_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS418play_81180.pat</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS418play_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS418play_72806.pat</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -11974,12 +11974,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS418play_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS418play_69057.pat</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -11996,12 +11996,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS418play_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS418play_64570.pat</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS418play_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS418play_42962.pat</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS418play_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS418play_42661.pat</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -12057,17 +12057,17 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>DS418play</t>
+          <t>DS718+</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS418play_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS718%2B_86009.pat</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS718%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS718%2B_42218.pat</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS718%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS718%2B_86003.pat</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS718%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS718%2B_81180.pat</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS718%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS718%2B_72806.pat</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -12172,12 +12172,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS718%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS718%2B_69057.pat</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS718%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS718%2B_64570.pat</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -12216,12 +12216,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS718%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS718%2B_42962.pat</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS718%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS718%2B_42661.pat</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -12255,17 +12255,17 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>DS718+</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS718%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS918%2B_86009.pat</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -12282,12 +12282,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS918%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS918%2B_42218.pat</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS918%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS918%2B_86003.pat</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS918%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS918%2B_81180.pat</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -12348,12 +12348,12 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS918%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS918%2B_72806.pat</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -12370,12 +12370,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS918%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS918%2B_69057.pat</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -12392,12 +12392,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS918%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS918%2B_64570.pat</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS918%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS918%2B_42962.pat</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS918%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS918%2B_42661.pat</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -12453,17 +12453,17 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS918%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS1018_86009.pat</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -12480,12 +12480,12 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS1018_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS1018_42218.pat</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS1018_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS1018_86003.pat</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS1018_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS1018_81180.pat</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -12546,12 +12546,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS1018_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS1018_72806.pat</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS1018_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS1018_69057.pat</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -12590,12 +12590,12 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS1018_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS1018_64570.pat</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS1018_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS1018_42962.pat</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS1018_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS1018_42661.pat</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -12651,17 +12651,17 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS1018_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2017_86009.pat</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2017_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2017_42218.pat</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -12700,12 +12700,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2017_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2017_86003.pat</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -12722,12 +12722,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2017_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2017_81180.pat</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2017_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2017_72806.pat</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -12766,12 +12766,12 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2017_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2017_69057.pat</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2017_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2017_64570.pat</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2017_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2017_42962.pat</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2017_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2017_42661.pat</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -12849,17 +12849,17 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2017_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS18017xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS18017xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS18017xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS18017xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS18017xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS18017xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS18017xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS18017xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS18017xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -12964,12 +12964,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS18017xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS18017xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS18017xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS18017xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -13008,12 +13008,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS18017xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS18017xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -13030,12 +13030,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS18017xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS18017xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -13047,17 +13047,17 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS18017xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418%2B_86009.pat</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -13074,12 +13074,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418%2B_42218.pat</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418%2B_86003.pat</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418%2B_81180.pat</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -13140,12 +13140,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418%2B_72806.pat</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -13162,12 +13162,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418%2B_69057.pat</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -13184,12 +13184,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418%2B_64570.pat</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418%2B_42962.pat</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -13228,12 +13228,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418%2B_42661.pat</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -13245,17 +13245,17 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -13294,12 +13294,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -13338,12 +13338,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -13360,12 +13360,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -13382,12 +13382,12 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -13404,12 +13404,12 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -13426,12 +13426,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -13443,17 +13443,17 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2818RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2818RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2818RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2818RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2818RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -13514,12 +13514,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2818RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2818RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -13536,12 +13536,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2818RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2818RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -13558,12 +13558,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2818RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2818RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -13580,12 +13580,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2818RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2818RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2818RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2818RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2818RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2818RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -13641,17 +13641,17 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2818RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617RPxs_86009.pat</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -13668,12 +13668,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617RPxs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617RPxs_42218.pat</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -13690,12 +13690,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617RPxs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617RPxs_86003.pat</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -13712,12 +13712,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617RPxs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617RPxs_81180.pat</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617RPxs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617RPxs_72806.pat</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617RPxs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617RPxs_69057.pat</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617RPxs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617RPxs_64570.pat</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617RPxs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617RPxs_42962.pat</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -13822,12 +13822,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617RPxs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617RPxs_42661.pat</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -13839,17 +13839,17 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617RPxs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -13866,12 +13866,12 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -13932,12 +13932,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -13976,12 +13976,12 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -14037,17 +14037,17 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS4017xs+</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4017xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4017xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4017xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -14086,12 +14086,12 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4017xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4017xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -14108,12 +14108,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4017xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4017xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -14130,12 +14130,12 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4017xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4017xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -14152,12 +14152,12 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4017xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4017xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -14174,12 +14174,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4017xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4017xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -14196,12 +14196,12 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4017xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4017xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -14218,37 +14218,15 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4017xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4017xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
-        <is>
-          <t>00000000000000000000000000000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>RS4017xs+</t>
-        </is>
-      </c>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>7.1.0-42661-1</t>
-        </is>
-      </c>
-      <c r="C629" t="inlineStr">
-        <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4017xs%2B_42661.pat</t>
-        </is>
-      </c>
-      <c r="D629" t="inlineStr">
         <is>
           <t>00000000000000000000000000000000</t>
         </is>

--- a/docs/pats.xlsx
+++ b/docs/pats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D628"/>
+  <dimension ref="A1:D629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SA6400</t>
+          <t>RS2423RP+II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA6400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2BII_86009.pat</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA6400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA6400_86009.pat</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -490,12 +490,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA6400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA6400_86003.pat</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -512,12 +512,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA6400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA6400_81180.pat</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -534,12 +534,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA6400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA6400_72806.pat</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -556,12 +556,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA6400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA6400_69057.pat</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA6400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA6400_64570.pat</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -595,17 +595,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DS1019+</t>
+          <t>SA6400</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1019%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA6400_42962.pat</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1019%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1019%2B_86009.pat</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1019%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1019%2B_42218.pat</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1019%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1019%2B_86003.pat</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1019%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1019%2B_81180.pat</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1019%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1019%2B_72806.pat</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1019%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1019%2B_69057.pat</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1019%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1019%2B_64570.pat</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1019%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1019%2B_42962.pat</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -793,17 +793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DS1520+</t>
+          <t>DS1019+</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1520%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1019%2B_42661.pat</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1520%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1520%2B_86009.pat</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1520%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1520%2B_42218.pat</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1520%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1520%2B_86003.pat</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1520%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1520%2B_81180.pat</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1520%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1520%2B_72806.pat</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1520%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1520%2B_69057.pat</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1520%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1520%2B_64570.pat</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1520%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1520%2B_42962.pat</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -991,17 +991,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DS1522+</t>
+          <t>DS1520+</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1522%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1520%2B_42661.pat</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1522%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1522%2B_86009.pat</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1522%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1522%2B_86003.pat</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1522%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1522%2B_81180.pat</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1522%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1522%2B_72806.pat</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1522%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1522%2B_69057.pat</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1522%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1522%2B_64570.pat</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1145,17 +1145,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DS1525+</t>
+          <t>DS1522+</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1525%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1522%2B_42962.pat</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1525%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1525%2B_86009.pat</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1525%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1525%2B_86003.pat</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1525%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1525%2B_81180.pat</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DS1621+</t>
+          <t>DS1525+</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1525%2B_72806.pat</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621%2B_86009.pat</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621%2B_42218.pat</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621%2B_86003.pat</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621%2B_81180.pat</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621%2B_72806.pat</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621%2B_69057.pat</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621%2B_64570.pat</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621%2B_42962.pat</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1431,17 +1431,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DS1621xs+</t>
+          <t>DS1621+</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621%2B_42661.pat</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1621xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1621xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1621xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1621xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1621xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1621xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1621xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1621xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1629,17 +1629,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DS1819+</t>
+          <t>DS1621xs+</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1819%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1621xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1819%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1819%2B_86009.pat</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1819%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1819%2B_42218.pat</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1819%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1819%2B_86003.pat</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1819%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1819%2B_81180.pat</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1819%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1819%2B_72806.pat</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1819%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1819%2B_69057.pat</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1819%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1819%2B_64570.pat</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1819%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1819%2B_42962.pat</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1827,17 +1827,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DS1821+</t>
+          <t>DS1819+</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1821%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1819%2B_42661.pat</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1821%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1821%2B_86009.pat</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1821%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1821%2B_42218.pat</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1821%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1821%2B_86003.pat</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1821%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1821%2B_81180.pat</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1821%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1821%2B_72806.pat</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1821%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1821%2B_69057.pat</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1821%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1821%2B_64570.pat</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1821%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1821%2B_42962.pat</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2025,17 +2025,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DS1823xs+</t>
+          <t>DS1821+</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1823xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1821%2B_42661.pat</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1823xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1823xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1823xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1823xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1823xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1823xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1823xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1823xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1823xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1823xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS1823xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1823xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2179,17 +2179,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DS1825+</t>
+          <t>DS1823xs+</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1825%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS1823xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1825%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1825%2B_86009.pat</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1825%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1825%2B_86003.pat</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1825%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1825%2B_81180.pat</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2267,17 +2267,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DS220+</t>
+          <t>DS1825+</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS220%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1825%2B_72806.pat</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS220%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS220%2B_86009.pat</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS220%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS220%2B_42218.pat</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS220%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS220%2B_86003.pat</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS220%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS220%2B_81180.pat</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS220%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS220%2B_72806.pat</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS220%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS220%2B_69057.pat</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS220%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS220%2B_64570.pat</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS220%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS220%2B_42962.pat</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2465,17 +2465,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DS224+</t>
+          <t>DS220+</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS224%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS220%2B_42661.pat</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS224%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS224%2B_86009.pat</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS224%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS224%2B_86003.pat</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS224%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS224%2B_81180.pat</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS224%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS224%2B_72806.pat</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2575,17 +2575,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DS225+</t>
+          <t>DS224+</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS225%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS224%2B_69057.pat</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS225%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS225%2B_86009.pat</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS225%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS225%2B_86003.pat</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS225%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS225%2B_81180.pat</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2663,17 +2663,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DS2419+</t>
+          <t>DS225+</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS225%2B_72806.pat</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2B_86009.pat</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2B_42218.pat</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2B_86003.pat</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2B_81180.pat</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2B_72806.pat</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2B_69057.pat</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2B_64570.pat</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2B_42962.pat</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2861,17 +2861,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DS2419+II</t>
+          <t>DS2419+</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2BII_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2B_42661.pat</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2BII_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2419%2BII_86009.pat</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2BII_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2419%2BII_42218.pat</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2BII_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2419%2BII_86003.pat</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2BII_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2419%2BII_81180.pat</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2BII_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2419%2BII_72806.pat</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2BII_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2419%2BII_69057.pat</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2BII_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2419%2BII_64570.pat</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2BII_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2419%2BII_42962.pat</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3059,17 +3059,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DS2422+</t>
+          <t>DS2419+II</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2422%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2419%2BII_42661.pat</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2422%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS2422%2B_86009.pat</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2422%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS2422%2B_86003.pat</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2422%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS2422%2B_81180.pat</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2422%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS2422%2B_72806.pat</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2422%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS2422%2B_69057.pat</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2422%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS2422%2B_64570.pat</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2422%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS2422%2B_42962.pat</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2422%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS2422%2B_42661.pat</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3257,17 +3257,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DS3622xs+</t>
+          <t>DS2422+</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3622xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS2422%2B_42218.pat</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3622xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3622xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3622xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3622xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3622xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3622xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3622xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3622xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3622xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3622xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3622xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3622xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3622xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3622xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3622xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3622xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3455,17 +3455,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DS420+</t>
+          <t>DS3622xs+</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS420%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3622xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS420%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS420%2B_86009.pat</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS420%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS420%2B_42218.pat</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS420%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS420%2B_86003.pat</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS420%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS420%2B_81180.pat</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS420%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS420%2B_72806.pat</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS420%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS420%2B_69057.pat</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS420%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS420%2B_64570.pat</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS420%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS420%2B_42962.pat</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3653,17 +3653,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DS423+</t>
+          <t>DS420+</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS423%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS420%2B_42661.pat</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS423%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS423%2B_86009.pat</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS423%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS423%2B_86003.pat</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS423%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS423%2B_81180.pat</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS423%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS423%2B_72806.pat</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS423%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS423%2B_69057.pat</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS423%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS423%2B_64570.pat</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3807,17 +3807,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DS425+</t>
+          <t>DS423+</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS425%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS423%2B_42962.pat</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS425%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS425%2B_86009.pat</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS425%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS425%2B_86003.pat</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS425%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS425%2B_81180.pat</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3895,17 +3895,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DS620slim</t>
+          <t>DS425+</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS620slim_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS425%2B_72806.pat</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS620slim_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS620slim_86009.pat</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS620slim_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS620slim_42218.pat</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS620slim_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS620slim_86003.pat</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS620slim_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS620slim_81180.pat</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_DS620slim_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS620slim_72806.pat</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS620slim_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_DS620slim_69057.pat</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS620slim_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS620slim_64570.pat</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS620slim_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS620slim_42962.pat</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4093,17 +4093,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DS720+</t>
+          <t>DS620slim</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS720%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS620slim_42661.pat</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS720%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS720%2B_86009.pat</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS720%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS720%2B_42218.pat</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS720%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS720%2B_86003.pat</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS720%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS720%2B_81180.pat</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS720%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS720%2B_72806.pat</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS720%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS720%2B_69057.pat</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS720%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS720%2B_64570.pat</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS720%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS720%2B_42962.pat</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4291,17 +4291,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DS723+</t>
+          <t>DS720+</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS723%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS720%2B_42661.pat</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS723%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS723%2B_86009.pat</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS723%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS723%2B_86003.pat</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS723%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS723%2B_81180.pat</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS723%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS723%2B_72806.pat</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS723%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS723%2B_69057.pat</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS723%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS723%2B_64570.pat</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4445,17 +4445,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DS725+</t>
+          <t>DS723+</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS725%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS723%2B_42962.pat</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4472,12 +4472,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS725%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS725%2B_86009.pat</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS725%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS725%2B_86003.pat</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS725%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS725%2B_81180.pat</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4533,17 +4533,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DS920+</t>
+          <t>DS725+</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS920%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS725%2B_72806.pat</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS920%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS920%2B_86009.pat</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS920%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS920%2B_42218.pat</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS920%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS920%2B_86003.pat</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS920%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS920%2B_81180.pat</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS920%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS920%2B_72806.pat</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS920%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS920%2B_69057.pat</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS920%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS920%2B_64570.pat</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS920%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS920%2B_42962.pat</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4731,17 +4731,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>DS923+</t>
+          <t>DS920+</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS923%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS920%2B_42661.pat</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS923%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS923%2B_86009.pat</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS923%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS923%2B_86003.pat</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS923%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS923%2B_81180.pat</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS923%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS923%2B_72806.pat</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS923%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS923%2B_69057.pat</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS923%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS923%2B_64570.pat</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4885,17 +4885,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DS925+</t>
+          <t>DS923+</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS925%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_DS923%2B_42962.pat</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS925%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS925%2B_86009.pat</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS925%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS925%2B_86003.pat</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS925%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS925%2B_81180.pat</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4973,17 +4973,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>DVA1622</t>
+          <t>DS925+</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA1622_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS925%2B_72806.pat</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA1622_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA1622_86009.pat</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA1622_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA1622_86003.pat</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA1622_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA1622_81180.pat</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA1622_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA1622_72806.pat</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA1622_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA1622_69057.pat</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA1622_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA1622_64570.pat</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5127,17 +5127,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>DVA3219</t>
+          <t>DVA1622</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3219_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA1622_42962.pat</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3219_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3219_86009.pat</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3219_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3219_42218.pat</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3219_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3219_86003.pat</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3219_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3219_81180.pat</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3219_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3219_72806.pat</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3219_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3219_69057.pat</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3219_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3219_64570.pat</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3219_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3219_42962.pat</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5325,17 +5325,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>DVA3221</t>
+          <t>DVA3219</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3221_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3219_42661.pat</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3221_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3221_86009.pat</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3221_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3221_42218.pat</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -5396,12 +5396,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3221_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3221_86003.pat</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3221_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3221_81180.pat</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3221_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3221_72806.pat</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3221_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3221_69057.pat</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3221_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3221_64570.pat</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3221_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3221_42962.pat</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5523,17 +5523,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>FS2500</t>
+          <t>DVA3221</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2500_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3221_42661.pat</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2500_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2500_86009.pat</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2500_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2500_86003.pat</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2500_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2500_81180.pat</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2500_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2500_72806.pat</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2500_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2500_69057.pat</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5660,12 +5660,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2500_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2500_64570.pat</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2500_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2500_42962.pat</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2500_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2500_42661.pat</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -5721,17 +5721,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>FS3400</t>
+          <t>FS2500</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2500_42218.pat</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3400_86009.pat</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3400_42218.pat</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3400_86003.pat</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3400_81180.pat</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3400_72806.pat</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3400_69057.pat</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3400_64570.pat</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3400_42962.pat</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -5919,17 +5919,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>FS3410</t>
+          <t>FS3400</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3410_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3400_42661.pat</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3410_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3410_86009.pat</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3410_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3410_86003.pat</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3410_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3410_81180.pat</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3410_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3410_72806.pat</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3410_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3410_69057.pat</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3410_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3410_64570.pat</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6073,17 +6073,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>FS3600</t>
+          <t>FS3410</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3410_42962.pat</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -6271,17 +6271,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FS6400</t>
+          <t>FS3600</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -6469,17 +6469,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>HD6500</t>
+          <t>FS6400</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_HD6500_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_HD6500_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_HD6500_86009.pat</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_HD6500_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_HD6500_86003.pat</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_HD6500_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_HD6500_81180.pat</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_HD6500_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_HD6500_72806.pat</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_HD6500_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_HD6500_69057.pat</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_HD6500_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_HD6500_64570.pat</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6623,17 +6623,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>RS1221+</t>
+          <t>HD6500</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_HD6500_42962.pat</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221%2B_86009.pat</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221%2B_42218.pat</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221%2B_86003.pat</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221%2B_81180.pat</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221%2B_72806.pat</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221%2B_69057.pat</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221%2B_64570.pat</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221%2B_42962.pat</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6821,17 +6821,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>RS1221RP+</t>
+          <t>RS1221+</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221%2B_42661.pat</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7019,17 +7019,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>RS1619xs+</t>
+          <t>RS1221RP+</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1619xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1619xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1619xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1619xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1619xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1619xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1619xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1619xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1619xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1619xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1619xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1619xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1619xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1619xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1619xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7200,12 +7200,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1619xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1619xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7217,17 +7217,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>RS2421+</t>
+          <t>RS1619xs+</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1619xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421%2B_86009.pat</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421%2B_42218.pat</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421%2B_86003.pat</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421%2B_81180.pat</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7332,12 +7332,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421%2B_72806.pat</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421%2B_69057.pat</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421%2B_64570.pat</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421%2B_42962.pat</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7415,17 +7415,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>RS2421RP+</t>
+          <t>RS2421+</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421%2B_42661.pat</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -7613,17 +7613,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>RS2423+</t>
+          <t>RS2421RP+</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423%2B_86009.pat</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423%2B_86003.pat</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -7684,12 +7684,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423%2B_81180.pat</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423%2B_72806.pat</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423%2B_69057.pat</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423%2B_64570.pat</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -7767,17 +7767,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>RS2423RP+</t>
+          <t>RS2423+</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423%2B_42962.pat</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -7794,12 +7794,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -7921,17 +7921,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>RS2821RP+</t>
+          <t>RS2423RP+</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2821RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2821RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2821RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2821RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2821RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2821RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2821RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2821RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2821RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2821RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2821RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2821RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2821RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2821RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2821RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2821RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2821RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -8119,17 +8119,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>RS2825RP+</t>
+          <t>RS2821RP+</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2825RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2821RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2825RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2825RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2825RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2825RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2825RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2825RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -8207,17 +8207,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>RS3618xs</t>
+          <t>RS2825RP+</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3618xs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2825RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3618xs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3618xs_86009.pat</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3618xs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3618xs_42218.pat</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3618xs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3618xs_86003.pat</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3618xs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3618xs_81180.pat</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3618xs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3618xs_72806.pat</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -8344,12 +8344,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3618xs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3618xs_69057.pat</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3618xs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3618xs_64570.pat</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3618xs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3618xs_42962.pat</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -8405,17 +8405,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>RS3621RPxs</t>
+          <t>RS3618xs</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621RPxs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3618xs_42661.pat</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621RPxs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621RPxs_86009.pat</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621RPxs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621RPxs_42218.pat</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621RPxs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621RPxs_86003.pat</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621RPxs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621RPxs_81180.pat</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621RPxs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621RPxs_72806.pat</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621RPxs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621RPxs_69057.pat</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621RPxs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621RPxs_64570.pat</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621RPxs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621RPxs_42962.pat</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -8603,17 +8603,17 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>RS3621xs+</t>
+          <t>RS3621RPxs</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621RPxs_42661.pat</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -8801,17 +8801,17 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>RS4021xs+</t>
+          <t>RS3621xs+</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4021xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4021xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4021xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4021xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4021xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4021xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4021xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4021xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4021xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4021xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4021xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4021xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4021xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4021xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4021xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4021xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4021xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -8999,17 +8999,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>RS422+</t>
+          <t>RS4021xs+</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS422%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4021xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS422%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS422%2B_86009.pat</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS422%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS422%2B_86003.pat</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS422%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS422%2B_81180.pat</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS422%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS422%2B_72806.pat</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -9114,12 +9114,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS422%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS422%2B_69057.pat</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS422%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS422%2B_64570.pat</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -9153,17 +9153,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>RS820+</t>
+          <t>RS422+</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS422%2B_42962.pat</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820%2B_86009.pat</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820%2B_42218.pat</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -9224,12 +9224,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820%2B_86003.pat</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -9246,12 +9246,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820%2B_81180.pat</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -9268,12 +9268,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820%2B_72806.pat</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820%2B_69057.pat</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820%2B_64570.pat</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820%2B_42962.pat</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -9351,17 +9351,17 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>RS820RP+</t>
+          <t>RS820+</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820%2B_42661.pat</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -9532,12 +9532,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -9549,17 +9549,17 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>RS822+</t>
+          <t>RS820RP+</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822%2B_86009.pat</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -9598,12 +9598,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822%2B_86003.pat</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822%2B_72806.pat</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822%2B_69057.pat</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822%2B_64570.pat</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -9681,17 +9681,17 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>RS822RP+</t>
+          <t>RS822+</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822%2B_42962.pat</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -9813,17 +9813,17 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>SA3200D</t>
+          <t>RS822RP+</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3200D_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3200D_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3200D_86009.pat</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3200D_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3200D_42218.pat</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3200D_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3200D_86003.pat</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3200D_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3200D_81180.pat</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3200D_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3200D_72806.pat</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3200D_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3200D_69057.pat</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3200D_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3200D_64570.pat</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3200D_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3200D_42962.pat</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -10011,17 +10011,17 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>SA3400</t>
+          <t>SA3200D</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3200D_42661.pat</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -10038,12 +10038,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400_86009.pat</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3400_42218.pat</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -10082,12 +10082,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400_86003.pat</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400_81180.pat</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400_72806.pat</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400_69057.pat</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400_64570.pat</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3400_42962.pat</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -10209,17 +10209,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>SA3400D</t>
+          <t>SA3400</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400D_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3400_42661.pat</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400D_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400D_86009.pat</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400D_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400D_86003.pat</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -10280,12 +10280,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400D_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400D_81180.pat</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400D_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400D_72806.pat</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400D_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400D_69057.pat</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3400D_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400D_64570.pat</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -10363,17 +10363,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>SA3410</t>
+          <t>SA3400D</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3410_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3400D_42962.pat</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3410_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3410_86009.pat</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -10412,12 +10412,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3410_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3410_86003.pat</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3410_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3410_81180.pat</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -10456,12 +10456,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3410_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3410_72806.pat</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3410_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3410_69057.pat</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -10500,12 +10500,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3410_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3410_64570.pat</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -10517,17 +10517,17 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>SA3600</t>
+          <t>SA3410</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3600_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3410_42962.pat</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -10544,12 +10544,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3600_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3600_86009.pat</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3600_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3600_42218.pat</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3600_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3600_86003.pat</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -10610,12 +10610,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3600_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3600_81180.pat</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3600_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3600_72806.pat</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3600_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3600_69057.pat</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3600_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3600_64570.pat</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3600_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3600_42962.pat</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -10715,17 +10715,17 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>SA3610</t>
+          <t>SA3600</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3610_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3600_42661.pat</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3610_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3610_86009.pat</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3610_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3610_86003.pat</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3610_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3610_81180.pat</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3610_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3610_72806.pat</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3610_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3610_69057.pat</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3610_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3610_64570.pat</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -10869,17 +10869,17 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>DS1618+</t>
+          <t>SA3610</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1618%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3610_42962.pat</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1618%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1618%2B_86009.pat</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1618%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1618%2B_42218.pat</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -10940,12 +10940,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1618%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1618%2B_86003.pat</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1618%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1618%2B_81180.pat</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1618%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1618%2B_72806.pat</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1618%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1618%2B_69057.pat</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1618%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1618%2B_64570.pat</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1618%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1618%2B_42962.pat</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -11067,17 +11067,17 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>DS218+</t>
+          <t>DS1618+</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS218%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1618%2B_42661.pat</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -11094,12 +11094,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS218%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS218%2B_86009.pat</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS218%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS218%2B_42218.pat</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS218%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS218%2B_86003.pat</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -11160,12 +11160,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS218%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS218%2B_81180.pat</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -11182,12 +11182,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS218%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS218%2B_72806.pat</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS218%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS218%2B_69057.pat</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -11226,12 +11226,12 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS218%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS218%2B_64570.pat</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS218%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS218%2B_42962.pat</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -11265,17 +11265,17 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>DS3018xs</t>
+          <t>DS218+</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3018xs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS218%2B_42661.pat</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -11292,12 +11292,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3018xs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3018xs_86009.pat</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -11314,12 +11314,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3018xs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3018xs_42218.pat</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3018xs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3018xs_86003.pat</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -11358,12 +11358,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3018xs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3018xs_81180.pat</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3018xs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3018xs_72806.pat</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -11402,12 +11402,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3018xs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3018xs_69057.pat</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3018xs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3018xs_64570.pat</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -11446,12 +11446,12 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3018xs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3018xs_42962.pat</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -11463,17 +11463,17 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>DS3617xs</t>
+          <t>DS3018xs</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3018xs_42661.pat</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xs_86009.pat</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xs_42218.pat</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xs_86003.pat</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -11556,12 +11556,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xs_81180.pat</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xs_72806.pat</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -11600,12 +11600,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xs_69057.pat</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xs_64570.pat</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -11644,12 +11644,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xs_42962.pat</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -11661,17 +11661,17 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>DS3617xsII</t>
+          <t>DS3617xs</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xsII_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xs_42661.pat</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -11688,12 +11688,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xsII_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xsII_86009.pat</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -11710,12 +11710,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xsII_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xsII_42218.pat</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -11732,12 +11732,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xsII_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xsII_86003.pat</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xsII_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xsII_81180.pat</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xsII_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xsII_72806.pat</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xsII_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xsII_69057.pat</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xsII_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xsII_64570.pat</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xsII_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xsII_42962.pat</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -11859,17 +11859,17 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>DS418play</t>
+          <t>DS3617xsII</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS418play_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xsII_42661.pat</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -11886,12 +11886,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS418play_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS418play_86009.pat</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS418play_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS418play_42218.pat</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS418play_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS418play_86003.pat</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS418play_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS418play_81180.pat</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -11974,12 +11974,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS418play_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS418play_72806.pat</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -11996,12 +11996,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS418play_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS418play_69057.pat</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS418play_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS418play_64570.pat</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -12040,12 +12040,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS418play_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS418play_42962.pat</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -12057,17 +12057,17 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>DS718+</t>
+          <t>DS418play</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS718%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS418play_42661.pat</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS718%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS718%2B_86009.pat</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS718%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS718%2B_42218.pat</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS718%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS718%2B_86003.pat</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS718%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS718%2B_81180.pat</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -12172,12 +12172,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS718%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS718%2B_72806.pat</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS718%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS718%2B_69057.pat</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -12216,12 +12216,12 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS718%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS718%2B_64570.pat</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS718%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS718%2B_42962.pat</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -12255,17 +12255,17 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>DS718+</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS918%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS718%2B_42661.pat</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -12282,12 +12282,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS918%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS918%2B_86009.pat</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS918%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS918%2B_42218.pat</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS918%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS918%2B_86003.pat</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -12348,12 +12348,12 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS918%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS918%2B_81180.pat</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -12370,12 +12370,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS918%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS918%2B_72806.pat</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -12392,12 +12392,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS918%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS918%2B_69057.pat</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS918%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS918%2B_64570.pat</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -12436,12 +12436,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS918%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS918%2B_42962.pat</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -12453,17 +12453,17 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS1018_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS918%2B_42661.pat</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -12480,12 +12480,12 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS1018_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS1018_86009.pat</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS1018_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS1018_42218.pat</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS1018_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS1018_86003.pat</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -12546,12 +12546,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS1018_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS1018_81180.pat</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS1018_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS1018_72806.pat</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -12590,12 +12590,12 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS1018_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS1018_69057.pat</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS1018_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS1018_64570.pat</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS1018_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS1018_42962.pat</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -12651,17 +12651,17 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2017_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS1018_42661.pat</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2017_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2017_86009.pat</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -12700,12 +12700,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2017_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2017_42218.pat</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -12722,12 +12722,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2017_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2017_86003.pat</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2017_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2017_81180.pat</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -12766,12 +12766,12 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2017_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2017_72806.pat</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2017_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2017_69057.pat</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2017_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2017_64570.pat</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2017_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2017_42962.pat</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -12849,17 +12849,17 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS18017xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2017_42661.pat</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS18017xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS18017xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS18017xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS18017xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS18017xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS18017xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS18017xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS18017xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -12964,12 +12964,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS18017xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS18017xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS18017xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS18017xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -13008,12 +13008,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS18017xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS18017xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -13030,12 +13030,12 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS18017xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS18017xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -13047,17 +13047,17 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS18017xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -13074,12 +13074,12 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418%2B_86009.pat</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418%2B_42218.pat</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418%2B_86003.pat</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -13140,12 +13140,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418%2B_81180.pat</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -13162,12 +13162,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418%2B_72806.pat</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -13184,12 +13184,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418%2B_69057.pat</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418%2B_64570.pat</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -13228,12 +13228,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418%2B_42962.pat</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -13245,17 +13245,17 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418%2B_42661.pat</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -13294,12 +13294,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -13338,12 +13338,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -13360,12 +13360,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -13382,12 +13382,12 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -13404,12 +13404,12 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -13426,12 +13426,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -13443,17 +13443,17 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2818RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2818RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2818RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -13492,12 +13492,12 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2818RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2818RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -13514,12 +13514,12 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2818RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2818RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -13536,12 +13536,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2818RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2818RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -13558,12 +13558,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2818RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2818RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -13580,12 +13580,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2818RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2818RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2818RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2818RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2818RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2818RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -13641,17 +13641,17 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617RPxs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2818RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -13668,12 +13668,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617RPxs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617RPxs_86009.pat</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -13690,12 +13690,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617RPxs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617RPxs_42218.pat</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -13712,12 +13712,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617RPxs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617RPxs_86003.pat</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617RPxs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617RPxs_81180.pat</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617RPxs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617RPxs_72806.pat</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617RPxs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617RPxs_69057.pat</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617RPxs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617RPxs_64570.pat</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -13822,12 +13822,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617RPxs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617RPxs_42962.pat</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -13839,17 +13839,17 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617RPxs_42661.pat</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -13866,12 +13866,12 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -13932,12 +13932,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -13976,12 +13976,12 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -14037,17 +14037,17 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>RS4017xs+</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4017xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4017xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4017xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -14086,12 +14086,12 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4017xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4017xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -14108,12 +14108,12 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4017xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4017xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -14130,12 +14130,12 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4017xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4017xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -14152,12 +14152,12 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4017xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4017xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -14174,12 +14174,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4017xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4017xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -14196,12 +14196,12 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4017xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4017xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -14218,15 +14218,37 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
+          <t>7.1.1-42962-1</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4017xs%2B_42962.pat</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>00000000000000000000000000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>RS4017xs+</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
           <t>7.1.0-42661-1</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C629" t="inlineStr">
         <is>
           <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4017xs%2B_42661.pat</t>
         </is>
       </c>
-      <c r="D628" t="inlineStr">
+      <c r="D629" t="inlineStr">
         <is>
           <t>00000000000000000000000000000000</t>
         </is>

--- a/docs/pats.xlsx
+++ b/docs/pats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D719"/>
+  <dimension ref="A1:D727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6931,7 +6931,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>FS3600</t>
+          <t>FS3420</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3600_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3420_90075.pat</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6953,17 +6953,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>FS3600</t>
+          <t>FS3420</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3420_86009.pat</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3600_90075.pat</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7151,17 +7151,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>FS6400</t>
+          <t>FS3600</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS6400_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7173,17 +7173,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>FS6400</t>
+          <t>FS3600</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7200,12 +7200,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS6400_90075.pat</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7332,12 +7332,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7371,17 +7371,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>HD6500</t>
+          <t>FS6400</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_HD6500_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7393,17 +7393,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>HD6500</t>
+          <t>FS6400</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_HD6500_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7415,17 +7415,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>HD6500</t>
+          <t>FS6420</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_HD6500_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS6420_90075.pat</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -7437,17 +7437,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>HD6500</t>
+          <t>FS6420</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_HD6500_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6420_86009.pat</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_HD6500_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_HD6500_90075.pat</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_HD6500_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_HD6500_86009.pat</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_HD6500_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_HD6500_86003.pat</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_HD6500_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_HD6500_81180.pat</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -7547,17 +7547,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>RS1221+</t>
+          <t>HD6500</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS1221%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_HD6500_72806.pat</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -7569,17 +7569,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>RS1221+</t>
+          <t>HD6500</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_HD6500_69057.pat</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -7591,17 +7591,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>RS1221+</t>
+          <t>HD6500</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_HD6500_64570.pat</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -7613,17 +7613,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>RS1221+</t>
+          <t>HD6500</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_HD6500_42962.pat</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS1221%2B_90075.pat</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221%2B_42218.pat</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -7684,12 +7684,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221%2B_86009.pat</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221%2B_86003.pat</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221%2B_81180.pat</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221%2B_72806.pat</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -7767,17 +7767,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>RS1221RP+</t>
+          <t>RS1221+</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS1221RP%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221%2B_69057.pat</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -7789,17 +7789,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>RS1221RP+</t>
+          <t>RS1221+</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221%2B_64570.pat</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -7811,17 +7811,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>RS1221RP+</t>
+          <t>RS1221+</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221%2B_42962.pat</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -7833,17 +7833,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>RS1221RP+</t>
+          <t>RS1221+</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221%2B_42661.pat</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS1221RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1221RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1221RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -7926,12 +7926,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1221RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1221RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1221RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -7987,17 +7987,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>RS1619xs+</t>
+          <t>RS1221RP+</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS1619xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1221RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -8009,17 +8009,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>RS1619xs+</t>
+          <t>RS1221RP+</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1619xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1221RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -8031,17 +8031,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>RS1619xs+</t>
+          <t>RS1221RP+</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1619xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1221RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -8053,17 +8053,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>RS1619xs+</t>
+          <t>RS1221RP+</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1619xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1221RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1619xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS1619xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1619xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS1619xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -8124,12 +8124,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1619xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1619xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1619xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS1619xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1619xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS1619xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1619xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS1619xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -8207,17 +8207,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>RS1626xs+</t>
+          <t>RS1619xs+</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS1626xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS1619xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -8229,17 +8229,17 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>RS1626xs+</t>
+          <t>RS1619xs+</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1626xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS1619xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -8251,17 +8251,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>RS2421+</t>
+          <t>RS1619xs+</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2421%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS1619xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -8273,17 +8273,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>RS2421+</t>
+          <t>RS1619xs+</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS1619xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -8295,17 +8295,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>RS2421+</t>
+          <t>RS1626xs+</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS1626xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -8317,17 +8317,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>RS2421+</t>
+          <t>RS1626xs+</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS1626xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -8344,12 +8344,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2421%2B_90075.pat</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421%2B_42218.pat</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421%2B_86009.pat</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421%2B_86003.pat</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421%2B_81180.pat</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421%2B_72806.pat</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -8471,17 +8471,17 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>RS2421RP+</t>
+          <t>RS2421+</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2421RP%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421%2B_69057.pat</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -8493,17 +8493,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>RS2421RP+</t>
+          <t>RS2421+</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421%2B_64570.pat</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -8515,17 +8515,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>RS2421RP+</t>
+          <t>RS2421+</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421%2B_42962.pat</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -8537,17 +8537,17 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>RS2421RP+</t>
+          <t>RS2421+</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421%2B_42661.pat</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2421RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2421RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2421RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2421RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2421RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2421RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -8691,17 +8691,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>RS2423+</t>
+          <t>RS2421RP+</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2423%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2421RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -8713,17 +8713,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>RS2423+</t>
+          <t>RS2421RP+</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2421RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -8735,17 +8735,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>RS2423+</t>
+          <t>RS2421RP+</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2421RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -8757,17 +8757,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>RS2423+</t>
+          <t>RS2421RP+</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2421RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2423%2B_90075.pat</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423%2B_86009.pat</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423%2B_86003.pat</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423%2B_81180.pat</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -8867,17 +8867,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>RS2423RP+</t>
+          <t>RS2423+</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2423RP%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423%2B_72806.pat</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -8889,17 +8889,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>RS2423RP+</t>
+          <t>RS2423+</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423%2B_69057.pat</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -8911,17 +8911,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>RS2423RP+</t>
+          <t>RS2423+</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423%2B_64570.pat</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -8933,17 +8933,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>RS2423RP+</t>
+          <t>RS2423+</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423%2B_42962.pat</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2423RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2423RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2423RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2423RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -9043,17 +9043,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>RS2821RP+</t>
+          <t>RS2423RP+</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2821RP%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2423RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -9065,17 +9065,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>RS2821RP+</t>
+          <t>RS2423RP+</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2821RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2423RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -9087,17 +9087,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>RS2821RP+</t>
+          <t>RS2423RP+</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2821RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2423RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -9109,17 +9109,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>RS2821RP+</t>
+          <t>RS2423RP+</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2821RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_RS2423RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2821RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2821RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -9158,12 +9158,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2821RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2821RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2821RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2821RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2821RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2821RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -9224,12 +9224,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2821RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2821RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -9246,12 +9246,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2821RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2821RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -9263,17 +9263,17 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>RS2825RP+</t>
+          <t>RS2821RP+</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2825RP%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2821RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -9285,17 +9285,17 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>RS2825RP+</t>
+          <t>RS2821RP+</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2825RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2821RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -9307,17 +9307,17 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>RS2825RP+</t>
+          <t>RS2821RP+</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2825RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2821RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -9329,17 +9329,17 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>RS2825RP+</t>
+          <t>RS2821RP+</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2825RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2821RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -9356,12 +9356,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2825RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2825RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -9373,17 +9373,17 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>RS3618xs</t>
+          <t>RS2825RP+</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3618xs_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2825RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -9395,17 +9395,17 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>RS3618xs</t>
+          <t>RS2825RP+</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3618xs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2825RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -9417,17 +9417,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>RS3618xs</t>
+          <t>RS2825RP+</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3618xs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2825RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -9439,17 +9439,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>RS3618xs</t>
+          <t>RS2825RP+</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3618xs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2825RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3618xs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3618xs_90075.pat</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3618xs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3618xs_42218.pat</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3618xs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3618xs_86009.pat</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -9532,12 +9532,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3618xs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3618xs_86003.pat</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3618xs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3618xs_81180.pat</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3618xs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3618xs_72806.pat</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -9593,17 +9593,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>RS3621RPxs</t>
+          <t>RS3618xs</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3621RPxs_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3618xs_69057.pat</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -9615,17 +9615,17 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>RS3621RPxs</t>
+          <t>RS3618xs</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621RPxs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3618xs_64570.pat</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -9637,17 +9637,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>RS3621RPxs</t>
+          <t>RS3618xs</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621RPxs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3618xs_42962.pat</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -9659,17 +9659,17 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>RS3621RPxs</t>
+          <t>RS3618xs</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621RPxs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3618xs_42661.pat</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621RPxs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3621RPxs_90075.pat</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621RPxs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621RPxs_42218.pat</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621RPxs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621RPxs_86009.pat</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621RPxs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621RPxs_86003.pat</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -9774,12 +9774,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621RPxs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621RPxs_81180.pat</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621RPxs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621RPxs_72806.pat</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -9813,17 +9813,17 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>RS3621xs+</t>
+          <t>RS3621RPxs</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3621xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621RPxs_69057.pat</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -9835,17 +9835,17 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>RS3621xs+</t>
+          <t>RS3621RPxs</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621RPxs_64570.pat</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -9857,17 +9857,17 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>RS3621xs+</t>
+          <t>RS3621RPxs</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621RPxs_42962.pat</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -9879,17 +9879,17 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>RS3621xs+</t>
+          <t>RS3621RPxs</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621RPxs_42661.pat</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3621xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3621xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3621xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -9972,12 +9972,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3621xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3621xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3621xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -10033,17 +10033,17 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>RS3626xs</t>
+          <t>RS3621xs+</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3626xs_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3621xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -10055,17 +10055,17 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>RS3626xs</t>
+          <t>RS3621xs+</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3626xs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3621xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -10077,17 +10077,17 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>RS4021xs+</t>
+          <t>RS3621xs+</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS4021xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3621xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -10099,17 +10099,17 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>RS4021xs+</t>
+          <t>RS3621xs+</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4021xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3621xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -10121,17 +10121,17 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>RS4021xs+</t>
+          <t>RS3626xs</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4021xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3626xs_90075.pat</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -10143,17 +10143,17 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>RS4021xs+</t>
+          <t>RS3626xs</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4021xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3626xs_86009.pat</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4021xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS4021xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4021xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4021xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -10214,12 +10214,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4021xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4021xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4021xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4021xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4021xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4021xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -10280,12 +10280,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4021xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4021xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -10297,17 +10297,17 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>RS422+</t>
+          <t>RS4021xs+</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS422%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4021xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -10319,17 +10319,17 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>RS422+</t>
+          <t>RS4021xs+</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS422%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4021xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -10341,17 +10341,17 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>RS422+</t>
+          <t>RS4021xs+</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS422%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4021xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -10363,17 +10363,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>RS422+</t>
+          <t>RS4021xs+</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS422%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4021xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS422%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS422%2B_90075.pat</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -10412,12 +10412,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS422%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS422%2B_86009.pat</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS422%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS422%2B_86003.pat</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -10456,12 +10456,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS422%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS422%2B_81180.pat</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -10473,17 +10473,17 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>RS4826xs+</t>
+          <t>RS422+</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS4826xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS422%2B_72806.pat</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -10495,17 +10495,17 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>RS4826xs+</t>
+          <t>RS422+</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4826xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS422%2B_69057.pat</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -10517,17 +10517,17 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>RS6426xs+</t>
+          <t>RS422+</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS6426xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS422%2B_64570.pat</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -10539,17 +10539,17 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>RS6426xs+</t>
+          <t>RS422+</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS6426xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS422%2B_42962.pat</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -10561,7 +10561,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>RS820+</t>
+          <t>RS4826xs+</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS820%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS4826xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -10583,17 +10583,17 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>RS820+</t>
+          <t>RS4826xs+</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4826xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -10605,17 +10605,17 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>RS820+</t>
+          <t>RS6426xs+</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS6426xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -10627,17 +10627,17 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>RS820+</t>
+          <t>RS6426xs+</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS6426xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS820%2B_90075.pat</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820%2B_42218.pat</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820%2B_86009.pat</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -10720,12 +10720,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820%2B_86003.pat</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820%2B_81180.pat</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820%2B_72806.pat</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -10781,17 +10781,17 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>RS820RP+</t>
+          <t>RS820+</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS820RP%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820%2B_69057.pat</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -10803,17 +10803,17 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>RS820RP+</t>
+          <t>RS820+</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820%2B_64570.pat</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -10825,17 +10825,17 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>RS820RP+</t>
+          <t>RS820+</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820%2B_42962.pat</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -10847,17 +10847,17 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>RS820RP+</t>
+          <t>RS820+</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820%2B_42661.pat</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -10874,12 +10874,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS820RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS820RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS820RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -10940,12 +10940,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS820RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS820RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS820RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -11001,17 +11001,17 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>RS822+</t>
+          <t>RS820RP+</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS822%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS820RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -11023,17 +11023,17 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>RS822+</t>
+          <t>RS820RP+</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS820RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -11045,17 +11045,17 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>RS822+</t>
+          <t>RS820RP+</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS820RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -11067,17 +11067,17 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>RS822+</t>
+          <t>RS820RP+</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS820RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -11094,12 +11094,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS822%2B_90075.pat</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822%2B_86009.pat</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822%2B_86003.pat</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -11155,17 +11155,17 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>RS822RP+</t>
+          <t>RS822+</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS822RP%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822%2B_72806.pat</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -11177,17 +11177,17 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>RS822RP+</t>
+          <t>RS822+</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822%2B_69057.pat</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -11199,17 +11199,17 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>RS822RP+</t>
+          <t>RS822+</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822%2B_64570.pat</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -11221,17 +11221,17 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>RS822RP+</t>
+          <t>RS822+</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822%2B_42962.pat</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS822RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS822RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -11292,12 +11292,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS822RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -11309,17 +11309,17 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>SA3200D</t>
+          <t>RS822RP+</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3200D_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS822RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -11331,17 +11331,17 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>SA3200D</t>
+          <t>RS822RP+</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3200D_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS822RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -11353,17 +11353,17 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>SA3200D</t>
+          <t>RS822RP+</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3200D_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS822RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -11375,17 +11375,17 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>SA3200D</t>
+          <t>RS822RP+</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3200D_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS822RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -11397,17 +11397,17 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>SA3200D</t>
+          <t>RS826+</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3200D_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS826%2B_90075.pat</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -11419,17 +11419,17 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>SA3200D</t>
+          <t>RS826+</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3200D_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS826%2B_86009.pat</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -11441,17 +11441,17 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>SA3200D</t>
+          <t>RS826RP+</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3200D_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS826RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -11463,17 +11463,17 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>SA3200D</t>
+          <t>RS826RP+</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3200D_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS826RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3200D_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3200D_90075.pat</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3200D_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3200D_42218.pat</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -11529,17 +11529,17 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>SA3400</t>
+          <t>SA3200D</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3400_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3200D_86009.pat</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -11551,17 +11551,17 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>SA3400</t>
+          <t>SA3200D</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3200D_86003.pat</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -11573,17 +11573,17 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>SA3400</t>
+          <t>SA3200D</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3200D_81180.pat</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -11595,17 +11595,17 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>SA3400</t>
+          <t>SA3200D</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3200D_72806.pat</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -11617,17 +11617,17 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>SA3400</t>
+          <t>SA3200D</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3200D_69057.pat</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -11639,17 +11639,17 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>SA3400</t>
+          <t>SA3200D</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3200D_64570.pat</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -11661,17 +11661,17 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>SA3400</t>
+          <t>SA3200D</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3200D_42962.pat</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -11683,17 +11683,17 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>SA3400</t>
+          <t>SA3200D</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3200D_42661.pat</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -11710,12 +11710,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3400_90075.pat</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -11732,12 +11732,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3400_42218.pat</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -11749,17 +11749,17 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>SA3400D</t>
+          <t>SA3400</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3400D_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400_86009.pat</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -11771,17 +11771,17 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>SA3400D</t>
+          <t>SA3400</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400D_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400_86003.pat</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -11793,17 +11793,17 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>SA3400D</t>
+          <t>SA3400</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400D_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400_81180.pat</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -11815,17 +11815,17 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>SA3400D</t>
+          <t>SA3400</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400D_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400_72806.pat</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -11837,17 +11837,17 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>SA3400D</t>
+          <t>SA3400</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400D_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400_69057.pat</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -11859,17 +11859,17 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>SA3400D</t>
+          <t>SA3400</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400D_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400_64570.pat</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -11881,17 +11881,17 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>SA3400D</t>
+          <t>SA3400</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400D_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3400_42962.pat</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -11903,17 +11903,17 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>SA3400D</t>
+          <t>SA3400</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3400D_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3400_42661.pat</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -11925,7 +11925,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>SA3410</t>
+          <t>SA3400D</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3410_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3400D_90075.pat</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -11947,7 +11947,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>SA3410</t>
+          <t>SA3400D</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3410_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3400D_86009.pat</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -11969,7 +11969,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>SA3410</t>
+          <t>SA3400D</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -11979,7 +11979,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3410_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3400D_86003.pat</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -11991,7 +11991,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>SA3410</t>
+          <t>SA3400D</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3410_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3400D_81180.pat</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -12013,7 +12013,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>SA3410</t>
+          <t>SA3400D</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3410_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3400D_72806.pat</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -12035,17 +12035,17 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>SA3410</t>
+          <t>SA3400D</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3410_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3400D_69057.pat</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -12057,7 +12057,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>SA3410</t>
+          <t>SA3400D</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3410_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3400D_64570.pat</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -12079,7 +12079,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>SA3410</t>
+          <t>SA3400D</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3410_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3400D_42962.pat</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -12101,7 +12101,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>SA3600</t>
+          <t>SA3410</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3600_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3410_90075.pat</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -12123,17 +12123,17 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>SA3600</t>
+          <t>SA3410</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3600_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3410_86009.pat</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -12145,17 +12145,17 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>SA3600</t>
+          <t>SA3410</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3600_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3410_86003.pat</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -12167,17 +12167,17 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>SA3600</t>
+          <t>SA3410</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3600_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3410_81180.pat</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -12189,17 +12189,17 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>SA3600</t>
+          <t>SA3410</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3600_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3410_72806.pat</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -12211,17 +12211,17 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>SA3600</t>
+          <t>SA3410</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3600_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3410_69057.pat</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -12233,17 +12233,17 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>SA3600</t>
+          <t>SA3410</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3600_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3410_64570.pat</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -12255,17 +12255,17 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>SA3600</t>
+          <t>SA3410</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3600_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3410_42962.pat</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -12282,12 +12282,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3600_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3600_90075.pat</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3600_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_SA3600_42218.pat</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -12321,17 +12321,17 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>SA3610</t>
+          <t>SA3600</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3610_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3600_86009.pat</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -12343,17 +12343,17 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>SA3610</t>
+          <t>SA3600</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3610_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3600_86003.pat</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -12365,17 +12365,17 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>SA3610</t>
+          <t>SA3600</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3610_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3600_81180.pat</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -12387,17 +12387,17 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>SA3610</t>
+          <t>SA3600</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3610_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3600_72806.pat</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -12409,17 +12409,17 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>SA3610</t>
+          <t>SA3600</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3610_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_SA3600_69057.pat</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -12431,17 +12431,17 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>SA3610</t>
+          <t>SA3600</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3610_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3600_64570.pat</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -12453,17 +12453,17 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>SA3610</t>
+          <t>SA3600</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3610_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_SA3600_42962.pat</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -12475,17 +12475,17 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>SA3610</t>
+          <t>SA3600</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>7.1.1-42962-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3610_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_SA3600_42661.pat</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -12497,7 +12497,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>DS1618+</t>
+          <t>SA3610</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1618%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_SA3610_90075.pat</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -12519,17 +12519,17 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>DS1618+</t>
+          <t>SA3610</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1618%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_SA3610_86009.pat</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -12541,17 +12541,17 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>DS1618+</t>
+          <t>SA3610</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1618%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_SA3610_86003.pat</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -12563,17 +12563,17 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>DS1618+</t>
+          <t>SA3610</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1618%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_SA3610_81180.pat</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -12585,17 +12585,17 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>DS1618+</t>
+          <t>SA3610</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1618%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_SA3610_72806.pat</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -12607,17 +12607,17 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>DS1618+</t>
+          <t>SA3610</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1618%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_SA3610_69057.pat</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -12629,17 +12629,17 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>DS1618+</t>
+          <t>SA3610</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1618%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_SA3610_64570.pat</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -12651,17 +12651,17 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>DS1618+</t>
+          <t>SA3610</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.1-42962-0</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1618%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962/DSM_SA3610_42962.pat</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1618%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS1618%2B_90075.pat</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -12700,12 +12700,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1618%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS1618%2B_42218.pat</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -12717,17 +12717,17 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>DS218+</t>
+          <t>DS1618+</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS218%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS1618%2B_86009.pat</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -12739,17 +12739,17 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>DS218+</t>
+          <t>DS1618+</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS218%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS1618%2B_86003.pat</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -12761,17 +12761,17 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>DS218+</t>
+          <t>DS1618+</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS218%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS1618%2B_81180.pat</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -12783,17 +12783,17 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>DS218+</t>
+          <t>DS1618+</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS218%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS1618%2B_72806.pat</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -12805,17 +12805,17 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>DS218+</t>
+          <t>DS1618+</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS218%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS1618%2B_69057.pat</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -12827,17 +12827,17 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>DS218+</t>
+          <t>DS1618+</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS218%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS1618%2B_64570.pat</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -12849,17 +12849,17 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>DS218+</t>
+          <t>DS1618+</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS218%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS1618%2B_42962.pat</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -12871,17 +12871,17 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>DS218+</t>
+          <t>DS1618+</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS218%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS1618%2B_42661.pat</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS218%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS218%2B_90075.pat</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS218%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS218%2B_42218.pat</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -12937,17 +12937,17 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>DS3018xs</t>
+          <t>DS218+</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS3018xs_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS218%2B_86009.pat</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -12959,17 +12959,17 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>DS3018xs</t>
+          <t>DS218+</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3018xs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS218%2B_86003.pat</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -12981,17 +12981,17 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>DS3018xs</t>
+          <t>DS218+</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3018xs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS218%2B_81180.pat</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -13003,17 +13003,17 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>DS3018xs</t>
+          <t>DS218+</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3018xs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS218%2B_72806.pat</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -13025,17 +13025,17 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>DS3018xs</t>
+          <t>DS218+</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3018xs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS218%2B_69057.pat</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -13047,17 +13047,17 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>DS3018xs</t>
+          <t>DS218+</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3018xs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS218%2B_64570.pat</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -13069,17 +13069,17 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>DS3018xs</t>
+          <t>DS218+</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3018xs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS218%2B_42962.pat</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -13091,17 +13091,17 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>DS3018xs</t>
+          <t>DS218+</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3018xs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS218%2B_42661.pat</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3018xs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS3018xs_90075.pat</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -13140,12 +13140,12 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3018xs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3018xs_42218.pat</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -13157,17 +13157,17 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>DS3617xs</t>
+          <t>DS3018xs</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS3617xs_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3018xs_86009.pat</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -13179,17 +13179,17 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>DS3617xs</t>
+          <t>DS3018xs</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3018xs_86003.pat</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -13201,17 +13201,17 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>DS3617xs</t>
+          <t>DS3018xs</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3018xs_81180.pat</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -13223,17 +13223,17 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>DS3617xs</t>
+          <t>DS3018xs</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3018xs_72806.pat</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -13245,17 +13245,17 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>DS3617xs</t>
+          <t>DS3018xs</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3018xs_69057.pat</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -13267,17 +13267,17 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>DS3617xs</t>
+          <t>DS3018xs</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3018xs_64570.pat</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -13289,17 +13289,17 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>DS3617xs</t>
+          <t>DS3018xs</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3018xs_42962.pat</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -13311,17 +13311,17 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>DS3617xs</t>
+          <t>DS3018xs</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3018xs_42661.pat</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -13338,12 +13338,12 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS3617xs_90075.pat</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -13360,12 +13360,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xs_42218.pat</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -13377,17 +13377,17 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>DS3617xsII</t>
+          <t>DS3617xs</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS3617xsII_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xs_86009.pat</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -13399,17 +13399,17 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>DS3617xsII</t>
+          <t>DS3617xs</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xsII_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xs_86003.pat</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -13421,17 +13421,17 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>DS3617xsII</t>
+          <t>DS3617xs</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xsII_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xs_81180.pat</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -13443,17 +13443,17 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>DS3617xsII</t>
+          <t>DS3617xs</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xsII_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xs_72806.pat</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -13465,17 +13465,17 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>DS3617xsII</t>
+          <t>DS3617xs</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xsII_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xs_69057.pat</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -13487,17 +13487,17 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>DS3617xsII</t>
+          <t>DS3617xs</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xsII_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xs_64570.pat</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -13509,17 +13509,17 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>DS3617xsII</t>
+          <t>DS3617xs</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xsII_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xs_42962.pat</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -13531,17 +13531,17 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>DS3617xsII</t>
+          <t>DS3617xs</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xsII_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xs_42661.pat</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -13558,12 +13558,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xsII_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS3617xsII_90075.pat</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -13580,12 +13580,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xsII_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS3617xsII_42218.pat</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -13597,17 +13597,17 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>DS418play</t>
+          <t>DS3617xsII</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS418play_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS3617xsII_86009.pat</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -13619,17 +13619,17 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>DS418play</t>
+          <t>DS3617xsII</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS418play_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS3617xsII_86003.pat</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -13641,17 +13641,17 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>DS418play</t>
+          <t>DS3617xsII</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS418play_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS3617xsII_81180.pat</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -13663,17 +13663,17 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>DS418play</t>
+          <t>DS3617xsII</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS418play_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS3617xsII_72806.pat</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -13685,17 +13685,17 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>DS418play</t>
+          <t>DS3617xsII</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS418play_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS3617xsII_69057.pat</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -13707,17 +13707,17 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>DS418play</t>
+          <t>DS3617xsII</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS418play_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS3617xsII_64570.pat</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -13729,17 +13729,17 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>DS418play</t>
+          <t>DS3617xsII</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS418play_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS3617xsII_42962.pat</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -13751,17 +13751,17 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>DS418play</t>
+          <t>DS3617xsII</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS418play_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS3617xsII_42661.pat</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS418play_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS418play_90075.pat</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -13800,12 +13800,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS418play_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS418play_42218.pat</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -13817,17 +13817,17 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>DS718+</t>
+          <t>DS418play</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS718%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS418play_86009.pat</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -13839,17 +13839,17 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>DS718+</t>
+          <t>DS418play</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS718%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS418play_86003.pat</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -13861,17 +13861,17 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>DS718+</t>
+          <t>DS418play</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS718%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS418play_81180.pat</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -13883,17 +13883,17 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>DS718+</t>
+          <t>DS418play</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS718%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS418play_72806.pat</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -13905,17 +13905,17 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>DS718+</t>
+          <t>DS418play</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS718%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS418play_69057.pat</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -13927,17 +13927,17 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>DS718+</t>
+          <t>DS418play</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS718%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS418play_64570.pat</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -13949,17 +13949,17 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>DS718+</t>
+          <t>DS418play</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS718%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS418play_42962.pat</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -13971,17 +13971,17 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>DS718+</t>
+          <t>DS418play</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS718%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS418play_42661.pat</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS718%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS718%2B_90075.pat</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS718%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS718%2B_42218.pat</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -14037,17 +14037,17 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>DS718+</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS918%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS718%2B_86009.pat</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -14059,17 +14059,17 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>DS718+</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS918%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS718%2B_86003.pat</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -14081,17 +14081,17 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>DS718+</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS918%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS718%2B_81180.pat</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -14103,17 +14103,17 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>DS718+</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS918%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS718%2B_72806.pat</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -14125,17 +14125,17 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>DS718+</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS918%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS718%2B_69057.pat</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -14147,17 +14147,17 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>DS718+</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS918%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS718%2B_64570.pat</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -14169,17 +14169,17 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>DS718+</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS918%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS718%2B_42962.pat</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -14191,17 +14191,17 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>DS918+</t>
+          <t>DS718+</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS918%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS718%2B_42661.pat</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS918%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DS918%2B_90075.pat</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -14240,12 +14240,12 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS918%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DS918%2B_42218.pat</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -14257,17 +14257,17 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS1018_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DS918%2B_86009.pat</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -14279,17 +14279,17 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS1018_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DS918%2B_86003.pat</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -14301,17 +14301,17 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS1018_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DS918%2B_81180.pat</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -14323,17 +14323,17 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS1018_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DS918%2B_72806.pat</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -14345,17 +14345,17 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS1018_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DS918%2B_69057.pat</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -14367,17 +14367,17 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS1018_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DS918%2B_64570.pat</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -14389,17 +14389,17 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS1018_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DS918%2B_42962.pat</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -14411,17 +14411,17 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>FS1018</t>
+          <t>DS918+</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS1018_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DS918%2B_42661.pat</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS1018_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS1018_90075.pat</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -14460,12 +14460,12 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS1018_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS1018_42218.pat</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -14477,17 +14477,17 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS2017_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS1018_86009.pat</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -14499,17 +14499,17 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2017_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS1018_86003.pat</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -14521,17 +14521,17 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2017_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS1018_81180.pat</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -14543,17 +14543,17 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2017_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS1018_72806.pat</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -14565,17 +14565,17 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2017_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS1018_69057.pat</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -14587,17 +14587,17 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2017_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS1018_64570.pat</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -14609,17 +14609,17 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2017_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS1018_42962.pat</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -14631,17 +14631,17 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>FS2017</t>
+          <t>FS1018</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2017_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS1018_42661.pat</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -14658,12 +14658,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2017_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS2017_90075.pat</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2017_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2017_42218.pat</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -14697,17 +14697,17 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS18017xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2017_86009.pat</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -14719,17 +14719,17 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS18017xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2017_86003.pat</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -14741,17 +14741,17 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS18017xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2017_81180.pat</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -14763,17 +14763,17 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS18017xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2017_72806.pat</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -14785,17 +14785,17 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS18017xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2017_69057.pat</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -14807,17 +14807,17 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS18017xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2017_64570.pat</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -14829,17 +14829,17 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS18017xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2017_42962.pat</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -14851,17 +14851,17 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>RS18017xs+</t>
+          <t>FS2017</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS18017xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2017_42661.pat</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -14878,12 +14878,12 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS18017xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS18017xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -14900,12 +14900,12 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS18017xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS18017xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -14917,17 +14917,17 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2418%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS18017xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -14939,17 +14939,17 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS18017xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -14961,17 +14961,17 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS18017xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -14983,17 +14983,17 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS18017xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -15005,17 +15005,17 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS18017xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -15027,17 +15027,17 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS18017xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -15049,17 +15049,17 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS18017xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -15071,17 +15071,17 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>RS2418+</t>
+          <t>RS18017xs+</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS18017xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -15098,12 +15098,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2418%2B_90075.pat</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418%2B_42218.pat</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -15137,17 +15137,17 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2418RP%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418%2B_86009.pat</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -15159,17 +15159,17 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418%2B_86003.pat</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -15181,17 +15181,17 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418%2B_81180.pat</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -15203,17 +15203,17 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418%2B_72806.pat</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -15225,17 +15225,17 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418%2B_69057.pat</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -15247,17 +15247,17 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418%2B_64570.pat</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -15269,17 +15269,17 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418%2B_42962.pat</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -15291,17 +15291,17 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>RS2418RP+</t>
+          <t>RS2418+</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418%2B_42661.pat</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
@@ -15318,12 +15318,12 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2418RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
@@ -15340,12 +15340,12 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2418RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
@@ -15357,17 +15357,17 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2818RP%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2418RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
@@ -15379,17 +15379,17 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2818RP%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2418RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
@@ -15401,17 +15401,17 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2818RP%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2418RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -15423,17 +15423,17 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2818RP%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2418RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
@@ -15445,17 +15445,17 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2818RP%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2418RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -15467,17 +15467,17 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2818RP%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2418RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -15489,17 +15489,17 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2818RP%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2418RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -15511,17 +15511,17 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>RS2818RP+</t>
+          <t>RS2418RP+</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2818RP%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2418RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2818RP%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS2818RP%2B_90075.pat</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2818RP%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS2818RP%2B_42218.pat</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -15577,17 +15577,17 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3617RPxs_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS2818RP%2B_86009.pat</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -15599,17 +15599,17 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617RPxs_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS2818RP%2B_86003.pat</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -15621,17 +15621,17 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617RPxs_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS2818RP%2B_81180.pat</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -15643,17 +15643,17 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617RPxs_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS2818RP%2B_72806.pat</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -15665,17 +15665,17 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617RPxs_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS2818RP%2B_69057.pat</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
@@ -15687,17 +15687,17 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617RPxs_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS2818RP%2B_64570.pat</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -15709,17 +15709,17 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617RPxs_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS2818RP%2B_42962.pat</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
@@ -15731,17 +15731,17 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>RS3617RPxs</t>
+          <t>RS2818RP+</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617RPxs_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS2818RP%2B_42661.pat</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
@@ -15758,12 +15758,12 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617RPxs_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3617RPxs_90075.pat</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
@@ -15780,12 +15780,12 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617RPxs_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617RPxs_42218.pat</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
@@ -15797,17 +15797,17 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3617xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617RPxs_86009.pat</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
@@ -15819,17 +15819,17 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617RPxs_86003.pat</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -15841,17 +15841,17 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617RPxs_81180.pat</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -15863,17 +15863,17 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617RPxs_72806.pat</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
@@ -15885,17 +15885,17 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617RPxs_69057.pat</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -15907,17 +15907,17 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617RPxs_64570.pat</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -15929,17 +15929,17 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617RPxs_42962.pat</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -15951,17 +15951,17 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>RS3617xs+</t>
+          <t>RS3617RPxs</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617RPxs_42661.pat</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -15978,12 +15978,12 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS3617xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -16000,12 +16000,12 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617xs%2B_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS3617xs%2B_42218.pat</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -16017,17 +16017,17 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>RS4017xs+</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS4017xs%2B_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS3617xs%2B_86009.pat</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -16039,17 +16039,17 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>RS4017xs+</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4017xs%2B_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS3617xs%2B_86003.pat</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -16061,17 +16061,17 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>RS4017xs+</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4017xs%2B_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS3617xs%2B_81180.pat</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -16083,17 +16083,17 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>RS4017xs+</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4017xs%2B_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS3617xs%2B_72806.pat</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -16105,17 +16105,17 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>RS4017xs+</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4017xs%2B_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS3617xs%2B_69057.pat</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -16127,17 +16127,17 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>RS4017xs+</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4017xs%2B_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS3617xs%2B_64570.pat</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -16149,17 +16149,17 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>RS4017xs+</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4017xs%2B_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS3617xs%2B_42962.pat</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -16171,17 +16171,17 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>RS4017xs+</t>
+          <t>RS3617xs+</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4017xs%2B_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS3617xs%2B_42661.pat</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -16198,12 +16198,12 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4017xs%2B_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_RS4017xs%2B_90075.pat</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -16220,15 +16220,191 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
+          <t>7.0.1-42218-0</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_RS4017xs%2B_42218.pat</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>00000000000000000000000000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>RS4017xs+</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>7.3.2-86009-0</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_RS4017xs%2B_86009.pat</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>00000000000000000000000000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>RS4017xs+</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>7.3.1-86003-0</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_RS4017xs%2B_86003.pat</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>00000000000000000000000000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>RS4017xs+</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>7.3.0-81180-0</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_RS4017xs%2B_81180.pat</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>00000000000000000000000000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>RS4017xs+</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>7.2.2-72806-0</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_RS4017xs%2B_72806.pat</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>00000000000000000000000000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>RS4017xs+</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>7.2.1-69057-1</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_RS4017xs%2B_69057.pat</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>00000000000000000000000000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>RS4017xs+</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>7.2.0-64570-1</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_RS4017xs%2B_64570.pat</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>00000000000000000000000000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>RS4017xs+</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>7.1.1-42962-1</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_RS4017xs%2B_42962.pat</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>00000000000000000000000000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>RS4017xs+</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
           <t>7.1.0-42661-1</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr">
+      <c r="C727" t="inlineStr">
         <is>
           <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_RS4017xs%2B_42661.pat</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr">
+      <c r="D727" t="inlineStr">
         <is>
           <t>00000000000000000000000000000000</t>
         </is>

--- a/docs/pats.xlsx
+++ b/docs/pats.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7.4.0-101188-0</t>
+          <t>7.4.0-101205-0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM_Enterprise/release/1.0/101188/DSM_Enterprise_PAS7700_101188.pat</t>
+          <t>https://global.synologydownload.com/download/DSM_Enterprise/release/1.0.1/101205/DSM_Enterprise_PAS7700_101205.pat</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/docs/pats.xlsx
+++ b/docs/pats.xlsx
@@ -6095,7 +6095,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>DVA1622</t>
+          <t>DS925neo+</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA1622_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DS925neo%2B_90080.pat</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA1622_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA1622_90080.pat</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA1622_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA1622_90075.pat</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA1622_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA1622_86009.pat</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA1622_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA1622_86003.pat</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA1622_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA1622_81180.pat</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA1622_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA1622_72806.pat</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA1622_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA1622_69057.pat</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA1622_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA1622_64570.pat</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -6293,17 +6293,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>DVA3219</t>
+          <t>DVA1622</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA3219_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA1622_42962.pat</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3219_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA3219_90080.pat</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -6342,12 +6342,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA3219_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3219_42218.pat</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3219_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA3219_90075.pat</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3219_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3219_86009.pat</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3219_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3219_86003.pat</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3219_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3219_81180.pat</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3219_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3219_72806.pat</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3219_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3219_69057.pat</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3219_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3219_64570.pat</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3219_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3219_42962.pat</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6535,17 +6535,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>DVA3221</t>
+          <t>DVA3219</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA3221_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3219_42661.pat</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3221_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA3221_90080.pat</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA3221_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_DVA3221_42218.pat</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3221_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_DVA3221_90075.pat</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3221_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_DVA3221_86009.pat</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3221_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_DVA3221_86003.pat</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3221_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_DVA3221_81180.pat</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3221_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_DVA3221_72806.pat</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3221_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_DVA3221_69057.pat</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3221_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_DVA3221_64570.pat</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3221_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_DVA3221_42962.pat</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6777,17 +6777,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>DVA7400</t>
+          <t>DVA3221</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA7400_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_DVA3221_42661.pat</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6799,7 +6799,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>FS200T</t>
+          <t>DVA7400</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS200T_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_DVA7400_90080.pat</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS200T_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS200T_90080.pat</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS200T_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS200T_90075.pat</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -6865,17 +6865,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>FS2500</t>
+          <t>FS200T</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS2500_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS200T_86009.pat</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS2500_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS2500_90080.pat</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2500_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS2500_90075.pat</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2500_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS2500_86009.pat</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2500_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS2500_86003.pat</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2500_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS2500_81180.pat</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2500_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS2500_72806.pat</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2500_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS2500_69057.pat</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2500_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS2500_64570.pat</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2500_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS2500_42962.pat</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7090,12 +7090,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2500_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS2500_42661.pat</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7107,17 +7107,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>FS3400</t>
+          <t>FS2500</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3400_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS2500_42218.pat</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3400_90080.pat</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3400_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3400_42218.pat</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3400_90075.pat</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7200,12 +7200,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3400_86009.pat</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3400_86003.pat</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3400_81180.pat</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3400_72806.pat</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3400_69057.pat</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3400_64570.pat</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7332,12 +7332,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3400_42962.pat</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7349,17 +7349,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>FS3410</t>
+          <t>FS3400</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3410_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3400_42661.pat</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7376,12 +7376,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3410_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3410_90080.pat</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3410_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3410_90075.pat</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3410_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3410_86009.pat</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3410_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3410_86003.pat</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3410_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3410_81180.pat</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3410_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3410_72806.pat</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3410_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3410_69057.pat</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3410_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3410_64570.pat</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -7547,17 +7547,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>FS3420</t>
+          <t>FS3410</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3420_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3410_42962.pat</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3420_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3420_90080.pat</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3420_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3420_90075.pat</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -7613,17 +7613,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>FS3600</t>
+          <t>FS3420</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3600_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3420_86009.pat</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS3600_90080.pat</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3600_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS3600_42218.pat</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -7684,12 +7684,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS3600_90075.pat</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS3600_86009.pat</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS3600_86003.pat</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS3600_81180.pat</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>7.2.1-69057-1</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS3600_72806.pat</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -7794,12 +7794,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-1</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057-1/DSM_FS3600_69057.pat</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS3600_64570.pat</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS3600_42962.pat</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -7855,17 +7855,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>FS6400</t>
+          <t>FS3600</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS6400_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS3600_42661.pat</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>7.0.1-42218-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS6400_90080.pat</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.0.1-42218-0</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS6400_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.0.1/42218/DSM_FS6400_42218.pat</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -7926,12 +7926,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>7.3.2-86009-0</t>
+          <t>7.4.0-90075-0</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS6400_90075.pat</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>7.3.1-86003-0</t>
+          <t>7.3.2-86009-0</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.2/86009/DSM_FS6400_86009.pat</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>7.3.0-81180-0</t>
+          <t>7.3.1-86003-0</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3.1/86003/DSM_FS6400_86003.pat</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>7.2.2-72806-0</t>
+          <t>7.3.0-81180-0</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.3/81180/DSM_FS6400_81180.pat</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>7.2.1-69057-0</t>
+          <t>7.2.2-72806-0</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.2/72806/DSM_FS6400_72806.pat</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>7.2.0-64570-1</t>
+          <t>7.2.1-69057-0</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2.1/69057/DSM_FS6400_69057.pat</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>7.1.1-42962-1</t>
+          <t>7.2.0-64570-1</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.2/64570-1/DSM_FS6400_64570.pat</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>7.1.0-42661-1</t>
+          <t>7.1.1-42962-1</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1.1/42962-1/DSM_FS6400_42962.pat</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -8097,17 +8097,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>FS6420</t>
+          <t>FS6400</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>7.4.1-90080-0</t>
+          <t>7.1.0-42661-1</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS6420_90080.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.1/42661-1/DSM_FS6400_42661.pat</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -8124,12 +8124,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>7.4.0-90075-0</t>
+          <t>7.4.1-90080-0</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>https://global.synologydownload.com/download/DSM/release/7.4/90075/DSM_FS6420_90075.pat</t>
+          <t>https://global.synologydownload.com/download/DSM/release/7.4.1/90080/DSM_FS6420_90080.pat</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
